--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/08,26/24,08,26 Останкино КИ и ЗПФ/дв 24,08,26 бррсч ост ки.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/08,26/24,08,26 Останкино КИ и ЗПФ/дв 24,08,26 бррсч ост ки.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\08,26\24,08,26 Останкино КИ и ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA32BA8A-C7A5-4728-92E4-364041D05FED}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA381DB4-8FFF-4859-B5A5-97678BE08295}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AF$111</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1103,7 +1103,8 @@
     <col min="21" max="30" width="6" style="15" customWidth="1"/>
     <col min="31" max="31" width="58.42578125" style="15" customWidth="1"/>
     <col min="32" max="32" width="7" style="15" customWidth="1"/>
-    <col min="33" max="48" width="3" style="15" customWidth="1"/>
+    <col min="33" max="33" width="10" style="15" customWidth="1"/>
+    <col min="34" max="48" width="3" style="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:48" x14ac:dyDescent="0.25">
@@ -1492,7 +1493,10 @@
         <f>SUM(AF6:AF497)</f>
         <v>8372.4500000000025</v>
       </c>
-      <c r="AG5" s="12"/>
+      <c r="AG5" s="3">
+        <f>SUM(AG6:AG497)</f>
+        <v>1754.4425999999999</v>
+      </c>
       <c r="AH5" s="12"/>
       <c r="AI5" s="12"/>
       <c r="AJ5" s="12"/>
@@ -1600,7 +1604,10 @@
         <f>G6*R6</f>
         <v>0</v>
       </c>
-      <c r="AG6" s="12"/>
+      <c r="AG6" s="12">
+        <f>P6*G6</f>
+        <v>0</v>
+      </c>
       <c r="AH6" s="12"/>
       <c r="AI6" s="12"/>
       <c r="AJ6" s="12"/>
@@ -1713,7 +1720,10 @@
         <f>G7*R7</f>
         <v>98.800000000000011</v>
       </c>
-      <c r="AG7" s="12"/>
+      <c r="AG7" s="12">
+        <f t="shared" ref="AG7:AG70" si="5">P7*G7</f>
+        <v>27.52</v>
+      </c>
       <c r="AH7" s="12"/>
       <c r="AI7" s="12"/>
       <c r="AJ7" s="12"/>
@@ -1780,11 +1790,11 @@
         <v>32.429600000000008</v>
       </c>
       <c r="R8" s="14">
-        <f t="shared" ref="R8:R71" si="5">ROUND(Q8,0)</f>
+        <f t="shared" ref="R8:R71" si="6">ROUND(Q8,0)</f>
         <v>32</v>
       </c>
       <c r="S8" s="12">
-        <f t="shared" ref="S8:S71" si="6">(F8+O8+R8)/P8</f>
+        <f t="shared" ref="S8:S71" si="7">(F8+O8+R8)/P8</f>
         <v>11.917650667075602</v>
       </c>
       <c r="T8" s="12">
@@ -1825,10 +1835,13 @@
         <v>42</v>
       </c>
       <c r="AF8" s="12">
-        <f t="shared" ref="AF8:AF71" si="7">G8*R8</f>
+        <f t="shared" ref="AF8:AF71" si="8">G8*R8</f>
         <v>32</v>
       </c>
-      <c r="AG8" s="12"/>
+      <c r="AG8" s="12">
+        <f t="shared" si="5"/>
+        <v>5.2168000000000001</v>
+      </c>
       <c r="AH8" s="12"/>
       <c r="AI8" s="12"/>
       <c r="AJ8" s="12"/>
@@ -1895,11 +1908,11 @@
         <v>581.79999999999995</v>
       </c>
       <c r="R9" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>582</v>
       </c>
       <c r="S9" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>11.002044989775051</v>
       </c>
       <c r="T9" s="12">
@@ -1940,10 +1953,13 @@
         <v>42</v>
       </c>
       <c r="AF9" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>145.5</v>
       </c>
-      <c r="AG9" s="12"/>
+      <c r="AG9" s="12">
+        <f t="shared" si="5"/>
+        <v>24.45</v>
+      </c>
       <c r="AH9" s="12"/>
       <c r="AI9" s="12"/>
       <c r="AJ9" s="12"/>
@@ -2007,11 +2023,11 @@
       </c>
       <c r="Q10" s="14"/>
       <c r="R10" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S10" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>16.274922379793573</v>
       </c>
       <c r="T10" s="12">
@@ -2050,10 +2066,13 @@
       </c>
       <c r="AE10" s="12"/>
       <c r="AF10" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AG10" s="12"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AG10" s="12">
+        <f t="shared" si="5"/>
+        <v>47.667999999999999</v>
+      </c>
       <c r="AH10" s="12"/>
       <c r="AI10" s="12"/>
       <c r="AJ10" s="12"/>
@@ -2116,15 +2135,15 @@
         <v>10.532</v>
       </c>
       <c r="Q11" s="14">
-        <f t="shared" ref="Q11:Q21" si="8">14*P11-O11-F11</f>
+        <f t="shared" ref="Q11:Q21" si="9">14*P11-O11-F11</f>
         <v>26.007000000000005</v>
       </c>
       <c r="R11" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>26</v>
       </c>
       <c r="S11" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>13.99933535890619</v>
       </c>
       <c r="T11" s="12">
@@ -2165,10 +2184,13 @@
         <v>42</v>
       </c>
       <c r="AF11" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>26</v>
       </c>
-      <c r="AG11" s="12"/>
+      <c r="AG11" s="12">
+        <f t="shared" si="5"/>
+        <v>10.532</v>
+      </c>
       <c r="AH11" s="12"/>
       <c r="AI11" s="12"/>
       <c r="AJ11" s="12"/>
@@ -2231,15 +2253,15 @@
         <v>5.4014000000000006</v>
       </c>
       <c r="Q12" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3.6576000000000022</v>
       </c>
       <c r="R12" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="S12" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>14.063390972710778</v>
       </c>
       <c r="T12" s="12">
@@ -2278,10 +2300,13 @@
       </c>
       <c r="AE12" s="12"/>
       <c r="AF12" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="AG12" s="12"/>
+      <c r="AG12" s="12">
+        <f t="shared" si="5"/>
+        <v>5.4014000000000006</v>
+      </c>
       <c r="AH12" s="12"/>
       <c r="AI12" s="12"/>
       <c r="AJ12" s="12"/>
@@ -2344,15 +2369,15 @@
         <v>59.633799999999994</v>
       </c>
       <c r="Q13" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>230.81619999999987</v>
       </c>
       <c r="R13" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>231</v>
       </c>
       <c r="S13" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>14.003082144689758</v>
       </c>
       <c r="T13" s="12">
@@ -2391,10 +2416,13 @@
       </c>
       <c r="AE13" s="12"/>
       <c r="AF13" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>231</v>
       </c>
-      <c r="AG13" s="12"/>
+      <c r="AG13" s="12">
+        <f t="shared" si="5"/>
+        <v>59.633799999999994</v>
+      </c>
       <c r="AH13" s="12"/>
       <c r="AI13" s="12"/>
       <c r="AJ13" s="12"/>
@@ -2461,11 +2489,11 @@
         <v>398.20000000000005</v>
       </c>
       <c r="R14" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>398</v>
       </c>
       <c r="S14" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>12.99715909090909</v>
       </c>
       <c r="T14" s="12">
@@ -2506,10 +2534,13 @@
         <v>42</v>
       </c>
       <c r="AF14" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>99.5</v>
       </c>
-      <c r="AG14" s="12"/>
+      <c r="AG14" s="12">
+        <f t="shared" si="5"/>
+        <v>17.600000000000001</v>
+      </c>
       <c r="AH14" s="12"/>
       <c r="AI14" s="12"/>
       <c r="AJ14" s="12"/>
@@ -2572,15 +2603,15 @@
         <v>19.493000000000002</v>
       </c>
       <c r="Q15" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>74.864000000000033</v>
       </c>
       <c r="R15" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>75</v>
       </c>
       <c r="S15" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>14.006976863489458</v>
       </c>
       <c r="T15" s="12">
@@ -2619,10 +2650,13 @@
       </c>
       <c r="AE15" s="12"/>
       <c r="AF15" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>75</v>
       </c>
-      <c r="AG15" s="12"/>
+      <c r="AG15" s="12">
+        <f t="shared" si="5"/>
+        <v>19.493000000000002</v>
+      </c>
       <c r="AH15" s="12"/>
       <c r="AI15" s="12"/>
       <c r="AJ15" s="12"/>
@@ -2689,11 +2723,11 @@
         <v>698</v>
       </c>
       <c r="R16" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>698</v>
       </c>
       <c r="S16" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="T16" s="12">
@@ -2734,10 +2768,13 @@
         <v>42</v>
       </c>
       <c r="AF16" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>174.5</v>
       </c>
-      <c r="AG16" s="12"/>
+      <c r="AG16" s="12">
+        <f t="shared" si="5"/>
+        <v>29.8</v>
+      </c>
       <c r="AH16" s="12"/>
       <c r="AI16" s="12"/>
       <c r="AJ16" s="12"/>
@@ -2800,15 +2837,15 @@
         <v>43.8</v>
       </c>
       <c r="Q17" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>259.19999999999993</v>
       </c>
       <c r="R17" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>259</v>
       </c>
       <c r="S17" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>13.995433789954339</v>
       </c>
       <c r="T17" s="12">
@@ -2847,10 +2884,13 @@
       </c>
       <c r="AE17" s="12"/>
       <c r="AF17" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>103.60000000000001</v>
       </c>
-      <c r="AG17" s="12"/>
+      <c r="AG17" s="12">
+        <f t="shared" si="5"/>
+        <v>17.52</v>
+      </c>
       <c r="AH17" s="12"/>
       <c r="AI17" s="12"/>
       <c r="AJ17" s="12"/>
@@ -2917,11 +2957,11 @@
         <v>251.46680000000003</v>
       </c>
       <c r="R18" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>251</v>
       </c>
       <c r="S18" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>12.989344801139476</v>
       </c>
       <c r="T18" s="12">
@@ -2960,10 +3000,13 @@
       </c>
       <c r="AE18" s="12"/>
       <c r="AF18" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>251</v>
       </c>
-      <c r="AG18" s="12"/>
+      <c r="AG18" s="12">
+        <f t="shared" si="5"/>
+        <v>43.809600000000003</v>
+      </c>
       <c r="AH18" s="12"/>
       <c r="AI18" s="12"/>
       <c r="AJ18" s="12"/>
@@ -3030,11 +3073,11 @@
         <v>62.374599999999994</v>
       </c>
       <c r="R19" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>62</v>
       </c>
       <c r="S19" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>8.9664619406593022</v>
       </c>
       <c r="T19" s="12">
@@ -3075,10 +3118,13 @@
         <v>42</v>
       </c>
       <c r="AF19" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>62</v>
       </c>
-      <c r="AG19" s="12"/>
+      <c r="AG19" s="12">
+        <f t="shared" si="5"/>
+        <v>11.1694</v>
+      </c>
       <c r="AH19" s="12"/>
       <c r="AI19" s="12"/>
       <c r="AJ19" s="12"/>
@@ -3140,11 +3186,11 @@
       </c>
       <c r="Q20" s="14"/>
       <c r="R20" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S20" s="12" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T20" s="12" t="e">
@@ -3185,10 +3231,13 @@
         <v>166</v>
       </c>
       <c r="AF20" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AG20" s="12"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AG20" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="AH20" s="12"/>
       <c r="AI20" s="12"/>
       <c r="AJ20" s="12"/>
@@ -3251,15 +3300,15 @@
         <v>38.0486</v>
       </c>
       <c r="Q21" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>239.20839999999998</v>
       </c>
       <c r="R21" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>239</v>
       </c>
       <c r="S21" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>13.994522794531203</v>
       </c>
       <c r="T21" s="12">
@@ -3298,10 +3347,13 @@
       </c>
       <c r="AE21" s="12"/>
       <c r="AF21" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>239</v>
       </c>
-      <c r="AG21" s="12"/>
+      <c r="AG21" s="12">
+        <f t="shared" si="5"/>
+        <v>38.0486</v>
+      </c>
       <c r="AH21" s="12"/>
       <c r="AI21" s="12"/>
       <c r="AJ21" s="12"/>
@@ -3368,11 +3420,11 @@
         <v>788.19999999999982</v>
       </c>
       <c r="R22" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>788</v>
       </c>
       <c r="S22" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>11.998502994011977</v>
       </c>
       <c r="T22" s="12">
@@ -3413,10 +3465,13 @@
         <v>42</v>
       </c>
       <c r="AF22" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>173.36</v>
       </c>
-      <c r="AG22" s="12"/>
+      <c r="AG22" s="12">
+        <f t="shared" si="5"/>
+        <v>29.391999999999999</v>
+      </c>
       <c r="AH22" s="12"/>
       <c r="AI22" s="12"/>
       <c r="AJ22" s="12"/>
@@ -3480,11 +3535,11 @@
         <v>10</v>
       </c>
       <c r="R23" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
       <c r="S23" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-176.79545454545456</v>
       </c>
       <c r="T23" s="12">
@@ -3525,10 +3580,13 @@
         <v>59</v>
       </c>
       <c r="AF23" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
-      <c r="AG23" s="12"/>
+      <c r="AG23" s="12">
+        <f t="shared" si="5"/>
+        <v>-0.17599999999999999</v>
+      </c>
       <c r="AH23" s="12"/>
       <c r="AI23" s="12"/>
       <c r="AJ23" s="12"/>
@@ -3590,11 +3648,11 @@
       </c>
       <c r="Q24" s="8"/>
       <c r="R24" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S24" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>16.242750621375311</v>
       </c>
       <c r="T24" s="6">
@@ -3635,10 +3693,13 @@
         <v>61</v>
       </c>
       <c r="AF24" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AG24" s="12"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AG24" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="AH24" s="12"/>
       <c r="AI24" s="12"/>
       <c r="AJ24" s="12"/>
@@ -3698,11 +3759,11 @@
       </c>
       <c r="Q25" s="8"/>
       <c r="R25" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S25" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T25" s="6">
@@ -3741,10 +3802,13 @@
       </c>
       <c r="AE25" s="6"/>
       <c r="AF25" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AG25" s="12"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AG25" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="AH25" s="12"/>
       <c r="AI25" s="12"/>
       <c r="AJ25" s="12"/>
@@ -3807,15 +3871,15 @@
         <v>10.1114</v>
       </c>
       <c r="Q26" s="14">
-        <f t="shared" ref="Q26" si="9">14*P26-O26-F26</f>
+        <f t="shared" ref="Q26" si="10">14*P26-O26-F26</f>
         <v>10.547599999999989</v>
       </c>
       <c r="R26" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="S26" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>14.044741578812035</v>
       </c>
       <c r="T26" s="12">
@@ -3854,10 +3918,13 @@
       </c>
       <c r="AE26" s="12"/>
       <c r="AF26" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>11</v>
       </c>
-      <c r="AG26" s="12"/>
+      <c r="AG26" s="12">
+        <f t="shared" si="5"/>
+        <v>10.1114</v>
+      </c>
       <c r="AH26" s="12"/>
       <c r="AI26" s="12"/>
       <c r="AJ26" s="12"/>
@@ -3924,11 +3991,11 @@
         <v>279.59999999999991</v>
       </c>
       <c r="R27" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>280</v>
       </c>
       <c r="S27" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>12.008196721311476</v>
       </c>
       <c r="T27" s="12">
@@ -3967,10 +4034,13 @@
       </c>
       <c r="AE27" s="12"/>
       <c r="AF27" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>25.2</v>
       </c>
-      <c r="AG27" s="12"/>
+      <c r="AG27" s="12">
+        <f t="shared" si="5"/>
+        <v>4.3919999999999995</v>
+      </c>
       <c r="AH27" s="12"/>
       <c r="AI27" s="12"/>
       <c r="AJ27" s="12"/>
@@ -4028,11 +4098,11 @@
       </c>
       <c r="Q28" s="8"/>
       <c r="R28" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S28" s="12" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T28" s="6" t="e">
@@ -4073,10 +4143,13 @@
         <v>37</v>
       </c>
       <c r="AF28" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AG28" s="12"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AG28" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="AH28" s="12"/>
       <c r="AI28" s="12"/>
       <c r="AJ28" s="12"/>
@@ -4140,11 +4213,11 @@
       </c>
       <c r="Q29" s="14"/>
       <c r="R29" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S29" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>72.222222222222214</v>
       </c>
       <c r="T29" s="12">
@@ -4183,10 +4256,13 @@
       </c>
       <c r="AE29" s="12"/>
       <c r="AF29" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AG29" s="12"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AG29" s="12">
+        <f t="shared" si="5"/>
+        <v>0.16200000000000001</v>
+      </c>
       <c r="AH29" s="12"/>
       <c r="AI29" s="12"/>
       <c r="AJ29" s="12"/>
@@ -4246,11 +4322,11 @@
       </c>
       <c r="Q30" s="14"/>
       <c r="R30" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S30" s="12" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T30" s="12" t="e">
@@ -4291,10 +4367,13 @@
         <v>47</v>
       </c>
       <c r="AF30" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AG30" s="12"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AG30" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="AH30" s="12"/>
       <c r="AI30" s="12"/>
       <c r="AJ30" s="12"/>
@@ -4357,15 +4436,15 @@
         <v>95.490800000000007</v>
       </c>
       <c r="Q31" s="14">
-        <f t="shared" ref="Q31:Q33" si="10">14*P31-O31-F31</f>
+        <f t="shared" ref="Q31:Q33" si="11">14*P31-O31-F31</f>
         <v>307.21920000000006</v>
       </c>
       <c r="R31" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>307</v>
       </c>
       <c r="S31" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>13.997704490903836</v>
       </c>
       <c r="T31" s="12">
@@ -4404,10 +4483,13 @@
       </c>
       <c r="AE31" s="12"/>
       <c r="AF31" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>307</v>
       </c>
-      <c r="AG31" s="12"/>
+      <c r="AG31" s="12">
+        <f t="shared" si="5"/>
+        <v>95.490800000000007</v>
+      </c>
       <c r="AH31" s="12"/>
       <c r="AI31" s="12"/>
       <c r="AJ31" s="12"/>
@@ -4470,15 +4552,15 @@
         <v>24</v>
       </c>
       <c r="Q32" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>117</v>
       </c>
       <c r="R32" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>117</v>
       </c>
       <c r="S32" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>14</v>
       </c>
       <c r="T32" s="12">
@@ -4517,10 +4599,13 @@
       </c>
       <c r="AE32" s="12"/>
       <c r="AF32" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>46.800000000000004</v>
       </c>
-      <c r="AG32" s="12"/>
+      <c r="AG32" s="12">
+        <f t="shared" si="5"/>
+        <v>9.6000000000000014</v>
+      </c>
       <c r="AH32" s="12"/>
       <c r="AI32" s="12"/>
       <c r="AJ32" s="12"/>
@@ -4583,15 +4668,15 @@
         <v>127.2</v>
       </c>
       <c r="Q33" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>716.8</v>
       </c>
       <c r="R33" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>717</v>
       </c>
       <c r="S33" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>14.001572327044025</v>
       </c>
       <c r="T33" s="12">
@@ -4630,10 +4715,13 @@
       </c>
       <c r="AE33" s="12"/>
       <c r="AF33" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>286.8</v>
       </c>
-      <c r="AG33" s="12"/>
+      <c r="AG33" s="12">
+        <f t="shared" si="5"/>
+        <v>50.88</v>
+      </c>
       <c r="AH33" s="12"/>
       <c r="AI33" s="12"/>
       <c r="AJ33" s="12"/>
@@ -4691,11 +4779,11 @@
       </c>
       <c r="Q34" s="8"/>
       <c r="R34" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S34" s="12" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T34" s="6" t="e">
@@ -4734,10 +4822,13 @@
       </c>
       <c r="AE34" s="6"/>
       <c r="AF34" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AG34" s="12"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AG34" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="AH34" s="12"/>
       <c r="AI34" s="12"/>
       <c r="AJ34" s="12"/>
@@ -4800,15 +4891,15 @@
         <v>104.8</v>
       </c>
       <c r="Q35" s="14">
-        <f t="shared" ref="Q35" si="11">14*P35-O35-F35</f>
+        <f t="shared" ref="Q35" si="12">14*P35-O35-F35</f>
         <v>505.20000000000005</v>
       </c>
       <c r="R35" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>505</v>
       </c>
       <c r="S35" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>13.998091603053435</v>
       </c>
       <c r="T35" s="12">
@@ -4847,10 +4938,13 @@
       </c>
       <c r="AE35" s="12"/>
       <c r="AF35" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>202</v>
       </c>
-      <c r="AG35" s="12"/>
+      <c r="AG35" s="12">
+        <f t="shared" si="5"/>
+        <v>41.92</v>
+      </c>
       <c r="AH35" s="12"/>
       <c r="AI35" s="12"/>
       <c r="AJ35" s="12"/>
@@ -4912,11 +5006,11 @@
       </c>
       <c r="Q36" s="14"/>
       <c r="R36" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S36" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>46.578947368421055</v>
       </c>
       <c r="T36" s="12">
@@ -4957,10 +5051,13 @@
         <v>167</v>
       </c>
       <c r="AF36" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AG36" s="12"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AG36" s="12">
+        <f t="shared" si="5"/>
+        <v>1.1399999999999999</v>
+      </c>
       <c r="AH36" s="12"/>
       <c r="AI36" s="12"/>
       <c r="AJ36" s="12"/>
@@ -5020,11 +5117,11 @@
       </c>
       <c r="Q37" s="8"/>
       <c r="R37" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S37" s="12" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T37" s="6" t="e">
@@ -5065,10 +5162,13 @@
         <v>77</v>
       </c>
       <c r="AF37" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AG37" s="12"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AG37" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="AH37" s="12"/>
       <c r="AI37" s="12"/>
       <c r="AJ37" s="12"/>
@@ -5116,7 +5216,7 @@
         <v>125</v>
       </c>
       <c r="L38" s="6">
-        <f t="shared" ref="L38:L69" si="12">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="13">E38-K38</f>
         <v>-125</v>
       </c>
       <c r="M38" s="6"/>
@@ -5125,20 +5225,20 @@
         <v>0</v>
       </c>
       <c r="P38" s="6">
-        <f t="shared" ref="P38:P69" si="13">E38/5</f>
+        <f t="shared" ref="P38:P69" si="14">E38/5</f>
         <v>0</v>
       </c>
       <c r="Q38" s="8"/>
       <c r="R38" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S38" s="12" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T38" s="6" t="e">
-        <f t="shared" ref="T38:T69" si="14">(F38+O38)/P38</f>
+        <f t="shared" ref="T38:T69" si="15">(F38+O38)/P38</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U38" s="6">
@@ -5175,10 +5275,13 @@
         <v>80</v>
       </c>
       <c r="AF38" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AG38" s="12"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AG38" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="AH38" s="12"/>
       <c r="AI38" s="12"/>
       <c r="AJ38" s="12"/>
@@ -5226,7 +5329,7 @@
         <v>70.8</v>
       </c>
       <c r="L39" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-25.327999999999996</v>
       </c>
       <c r="M39" s="6"/>
@@ -5235,20 +5338,20 @@
         <v>0</v>
       </c>
       <c r="P39" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>9.0944000000000003</v>
       </c>
       <c r="Q39" s="8"/>
       <c r="R39" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S39" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.4810212878254749</v>
       </c>
       <c r="T39" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1.4810212878254749</v>
       </c>
       <c r="U39" s="6">
@@ -5283,10 +5386,13 @@
       </c>
       <c r="AE39" s="6"/>
       <c r="AF39" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AG39" s="12"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AG39" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="AH39" s="12"/>
       <c r="AI39" s="12"/>
       <c r="AJ39" s="12"/>
@@ -5336,7 +5442,7 @@
         <v>310</v>
       </c>
       <c r="L40" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-180</v>
       </c>
       <c r="M40" s="12"/>
@@ -5345,7 +5451,7 @@
         <v>63</v>
       </c>
       <c r="P40" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>26</v>
       </c>
       <c r="Q40" s="14">
@@ -5353,15 +5459,15 @@
         <v>144</v>
       </c>
       <c r="R40" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>144</v>
       </c>
       <c r="S40" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="T40" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>6.4615384615384617</v>
       </c>
       <c r="U40" s="12">
@@ -5396,10 +5502,13 @@
       </c>
       <c r="AE40" s="12"/>
       <c r="AF40" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>43.199999999999996</v>
       </c>
-      <c r="AG40" s="12"/>
+      <c r="AG40" s="12">
+        <f t="shared" si="5"/>
+        <v>7.8</v>
+      </c>
       <c r="AH40" s="12"/>
       <c r="AI40" s="12"/>
       <c r="AJ40" s="12"/>
@@ -5449,7 +5558,7 @@
         <v>230.3</v>
       </c>
       <c r="L41" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4.1139999999999759</v>
       </c>
       <c r="M41" s="12"/>
@@ -5458,20 +5567,20 @@
         <v>0</v>
       </c>
       <c r="P41" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>46.882799999999996</v>
       </c>
       <c r="Q41" s="14"/>
       <c r="R41" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S41" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>14.328005153275829</v>
       </c>
       <c r="T41" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>14.328005153275829</v>
       </c>
       <c r="U41" s="12">
@@ -5508,10 +5617,13 @@
         <v>168</v>
       </c>
       <c r="AF41" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AG41" s="12"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AG41" s="12">
+        <f t="shared" si="5"/>
+        <v>46.882799999999996</v>
+      </c>
       <c r="AH41" s="12"/>
       <c r="AI41" s="12"/>
       <c r="AJ41" s="12"/>
@@ -5561,7 +5673,7 @@
         <v>116.1</v>
       </c>
       <c r="L42" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-61.855999999999995</v>
       </c>
       <c r="M42" s="12"/>
@@ -5570,20 +5682,20 @@
         <v>108</v>
       </c>
       <c r="P42" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>10.848800000000001</v>
       </c>
       <c r="Q42" s="14"/>
       <c r="R42" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S42" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>18.188463240174027</v>
       </c>
       <c r="T42" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>18.188463240174027</v>
       </c>
       <c r="U42" s="12">
@@ -5618,10 +5730,13 @@
       </c>
       <c r="AE42" s="12"/>
       <c r="AF42" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AG42" s="12"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AG42" s="12">
+        <f t="shared" si="5"/>
+        <v>10.848800000000001</v>
+      </c>
       <c r="AH42" s="12"/>
       <c r="AI42" s="12"/>
       <c r="AJ42" s="12"/>
@@ -5671,7 +5786,7 @@
         <v>126.1</v>
       </c>
       <c r="L43" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-4.438999999999993</v>
       </c>
       <c r="M43" s="12"/>
@@ -5680,7 +5795,7 @@
         <v>108</v>
       </c>
       <c r="P43" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>24.3322</v>
       </c>
       <c r="Q43" s="14">
@@ -5688,15 +5803,15 @@
         <v>158.07740000000001</v>
       </c>
       <c r="R43" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>158</v>
       </c>
       <c r="S43" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>11.996819029927421</v>
       </c>
       <c r="T43" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>5.503365910193077</v>
       </c>
       <c r="U43" s="12">
@@ -5731,10 +5846,13 @@
       </c>
       <c r="AE43" s="12"/>
       <c r="AF43" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>158</v>
       </c>
-      <c r="AG43" s="12"/>
+      <c r="AG43" s="12">
+        <f t="shared" si="5"/>
+        <v>24.3322</v>
+      </c>
       <c r="AH43" s="12"/>
       <c r="AI43" s="12"/>
       <c r="AJ43" s="12"/>
@@ -5784,7 +5902,7 @@
         <v>78</v>
       </c>
       <c r="L44" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-28.42</v>
       </c>
       <c r="M44" s="12"/>
@@ -5793,20 +5911,20 @@
         <v>119</v>
       </c>
       <c r="P44" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>9.9160000000000004</v>
       </c>
       <c r="Q44" s="14"/>
       <c r="R44" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S44" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>15.867083501411859</v>
       </c>
       <c r="T44" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>15.867083501411859</v>
       </c>
       <c r="U44" s="12">
@@ -5841,10 +5959,13 @@
       </c>
       <c r="AE44" s="12"/>
       <c r="AF44" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AG44" s="12"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AG44" s="12">
+        <f t="shared" si="5"/>
+        <v>9.9160000000000004</v>
+      </c>
       <c r="AH44" s="12"/>
       <c r="AI44" s="12"/>
       <c r="AJ44" s="12"/>
@@ -5894,7 +6015,7 @@
         <v>592</v>
       </c>
       <c r="L45" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-331</v>
       </c>
       <c r="M45" s="12"/>
@@ -5903,23 +6024,23 @@
         <v>683</v>
       </c>
       <c r="P45" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>52.2</v>
       </c>
       <c r="Q45" s="14">
-        <f t="shared" ref="Q45:Q48" si="15">14*P45-O45-F45</f>
+        <f t="shared" ref="Q45:Q48" si="16">14*P45-O45-F45</f>
         <v>42.800000000000068</v>
       </c>
       <c r="R45" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>43</v>
       </c>
       <c r="S45" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>14.00383141762452</v>
       </c>
       <c r="T45" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>13.18007662835249</v>
       </c>
       <c r="U45" s="12">
@@ -5954,10 +6075,13 @@
       </c>
       <c r="AE45" s="12"/>
       <c r="AF45" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>12.9</v>
       </c>
-      <c r="AG45" s="12"/>
+      <c r="AG45" s="12">
+        <f t="shared" si="5"/>
+        <v>15.66</v>
+      </c>
       <c r="AH45" s="12"/>
       <c r="AI45" s="12"/>
       <c r="AJ45" s="12"/>
@@ -5997,7 +6121,7 @@
         <v>11</v>
       </c>
       <c r="L46" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-11</v>
       </c>
       <c r="M46" s="12"/>
@@ -6006,20 +6130,20 @@
         <v>50</v>
       </c>
       <c r="P46" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Q46" s="14"/>
       <c r="R46" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S46" s="12" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T46" s="12" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U46" s="12">
@@ -6056,10 +6180,13 @@
         <v>89</v>
       </c>
       <c r="AF46" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AG46" s="12"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AG46" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="AH46" s="12"/>
       <c r="AI46" s="12"/>
       <c r="AJ46" s="12"/>
@@ -6109,7 +6236,7 @@
         <v>118.5</v>
       </c>
       <c r="L47" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-34.119</v>
       </c>
       <c r="M47" s="12"/>
@@ -6118,23 +6245,23 @@
         <v>0</v>
       </c>
       <c r="P47" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>16.876200000000001</v>
       </c>
       <c r="Q47" s="14">
+        <f t="shared" si="16"/>
+        <v>107.15380000000002</v>
+      </c>
+      <c r="R47" s="14">
+        <f t="shared" si="6"/>
+        <v>107</v>
+      </c>
+      <c r="S47" s="12">
+        <f t="shared" si="7"/>
+        <v>13.990886573991775</v>
+      </c>
+      <c r="T47" s="12">
         <f t="shared" si="15"/>
-        <v>107.15380000000002</v>
-      </c>
-      <c r="R47" s="14">
-        <f t="shared" si="5"/>
-        <v>107</v>
-      </c>
-      <c r="S47" s="12">
-        <f t="shared" si="6"/>
-        <v>13.990886573991775</v>
-      </c>
-      <c r="T47" s="12">
-        <f t="shared" si="14"/>
         <v>7.6505966983088607</v>
       </c>
       <c r="U47" s="12">
@@ -6169,10 +6296,13 @@
       </c>
       <c r="AE47" s="12"/>
       <c r="AF47" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>107</v>
       </c>
-      <c r="AG47" s="12"/>
+      <c r="AG47" s="12">
+        <f t="shared" si="5"/>
+        <v>16.876200000000001</v>
+      </c>
       <c r="AH47" s="12"/>
       <c r="AI47" s="12"/>
       <c r="AJ47" s="12"/>
@@ -6222,7 +6352,7 @@
         <v>1033</v>
       </c>
       <c r="L48" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-240</v>
       </c>
       <c r="M48" s="12"/>
@@ -6231,23 +6361,23 @@
         <v>1031</v>
       </c>
       <c r="P48" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>158.6</v>
       </c>
       <c r="Q48" s="14">
+        <f t="shared" si="16"/>
+        <v>819.40000000000009</v>
+      </c>
+      <c r="R48" s="14">
+        <f t="shared" si="6"/>
+        <v>819</v>
+      </c>
+      <c r="S48" s="12">
+        <f t="shared" si="7"/>
+        <v>13.997477931904163</v>
+      </c>
+      <c r="T48" s="12">
         <f t="shared" si="15"/>
-        <v>819.40000000000009</v>
-      </c>
-      <c r="R48" s="14">
-        <f t="shared" si="5"/>
-        <v>819</v>
-      </c>
-      <c r="S48" s="12">
-        <f t="shared" si="6"/>
-        <v>13.997477931904163</v>
-      </c>
-      <c r="T48" s="12">
-        <f t="shared" si="14"/>
         <v>8.833543505674653</v>
       </c>
       <c r="U48" s="12">
@@ -6282,10 +6412,13 @@
       </c>
       <c r="AE48" s="12"/>
       <c r="AF48" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>286.64999999999998</v>
       </c>
-      <c r="AG48" s="12"/>
+      <c r="AG48" s="12">
+        <f t="shared" si="5"/>
+        <v>55.51</v>
+      </c>
       <c r="AH48" s="12"/>
       <c r="AI48" s="12"/>
       <c r="AJ48" s="12"/>
@@ -6335,7 +6468,7 @@
         <v>487</v>
       </c>
       <c r="L49" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-501</v>
       </c>
       <c r="M49" s="12"/>
@@ -6344,22 +6477,22 @@
         <v>322</v>
       </c>
       <c r="P49" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-2.8</v>
       </c>
       <c r="Q49" s="14">
         <v>150</v>
       </c>
       <c r="R49" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>150</v>
       </c>
       <c r="S49" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-172.5</v>
       </c>
       <c r="T49" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-118.92857142857143</v>
       </c>
       <c r="U49" s="12">
@@ -6396,10 +6529,13 @@
         <v>169</v>
       </c>
       <c r="AF49" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>61.499999999999993</v>
       </c>
-      <c r="AG49" s="12"/>
+      <c r="AG49" s="12">
+        <f t="shared" si="5"/>
+        <v>-1.1479999999999999</v>
+      </c>
       <c r="AH49" s="12"/>
       <c r="AI49" s="12"/>
       <c r="AJ49" s="12"/>
@@ -6449,7 +6585,7 @@
         <v>432</v>
       </c>
       <c r="L50" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-349</v>
       </c>
       <c r="M50" s="12"/>
@@ -6458,20 +6594,20 @@
         <v>364</v>
       </c>
       <c r="P50" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>16.600000000000001</v>
       </c>
       <c r="Q50" s="14"/>
       <c r="R50" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S50" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>39.578313253012048</v>
       </c>
       <c r="T50" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>39.578313253012048</v>
       </c>
       <c r="U50" s="12">
@@ -6506,10 +6642,13 @@
       </c>
       <c r="AE50" s="12"/>
       <c r="AF50" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AG50" s="12"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AG50" s="12">
+        <f t="shared" si="5"/>
+        <v>6.806</v>
+      </c>
       <c r="AH50" s="12"/>
       <c r="AI50" s="12"/>
       <c r="AJ50" s="12"/>
@@ -6553,7 +6692,7 @@
       <c r="J51" s="6"/>
       <c r="K51" s="6"/>
       <c r="L51" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="M51" s="6"/>
@@ -6562,20 +6701,20 @@
         <v>0</v>
       </c>
       <c r="P51" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Q51" s="8"/>
       <c r="R51" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S51" s="12" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T51" s="6" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U51" s="6">
@@ -6612,10 +6751,13 @@
         <v>47</v>
       </c>
       <c r="AF51" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AG51" s="12"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AG51" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="AH51" s="12"/>
       <c r="AI51" s="12"/>
       <c r="AJ51" s="12"/>
@@ -6663,7 +6805,7 @@
         <v>93</v>
       </c>
       <c r="L52" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-59</v>
       </c>
       <c r="M52" s="12"/>
@@ -6672,7 +6814,7 @@
         <v>30</v>
       </c>
       <c r="P52" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>6.8</v>
       </c>
       <c r="Q52" s="14">
@@ -6680,15 +6822,15 @@
         <v>42.8</v>
       </c>
       <c r="R52" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>43</v>
       </c>
       <c r="S52" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>11.029411764705882</v>
       </c>
       <c r="T52" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>4.7058823529411766</v>
       </c>
       <c r="U52" s="12">
@@ -6725,10 +6867,13 @@
         <v>96</v>
       </c>
       <c r="AF52" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>15.479999999999999</v>
       </c>
-      <c r="AG52" s="12"/>
+      <c r="AG52" s="12">
+        <f t="shared" si="5"/>
+        <v>2.448</v>
+      </c>
       <c r="AH52" s="12"/>
       <c r="AI52" s="12"/>
       <c r="AJ52" s="12"/>
@@ -6778,7 +6923,7 @@
         <v>171</v>
       </c>
       <c r="L53" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-145</v>
       </c>
       <c r="M53" s="12"/>
@@ -6787,20 +6932,20 @@
         <v>168</v>
       </c>
       <c r="P53" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5.2</v>
       </c>
       <c r="Q53" s="14"/>
       <c r="R53" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S53" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>48.846153846153847</v>
       </c>
       <c r="T53" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>48.846153846153847</v>
       </c>
       <c r="U53" s="12">
@@ -6837,10 +6982,13 @@
         <v>98</v>
       </c>
       <c r="AF53" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AG53" s="12"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AG53" s="12">
+        <f t="shared" si="5"/>
+        <v>1.7160000000000002</v>
+      </c>
       <c r="AH53" s="12"/>
       <c r="AI53" s="12"/>
       <c r="AJ53" s="12"/>
@@ -6890,7 +7038,7 @@
         <v>280</v>
       </c>
       <c r="L54" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-90</v>
       </c>
       <c r="M54" s="12"/>
@@ -6899,23 +7047,23 @@
         <v>295</v>
       </c>
       <c r="P54" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>38</v>
       </c>
       <c r="Q54" s="14">
-        <f t="shared" ref="Q54" si="16">14*P54-O54-F54</f>
+        <f t="shared" ref="Q54" si="17">14*P54-O54-F54</f>
         <v>183</v>
       </c>
       <c r="R54" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>183</v>
       </c>
       <c r="S54" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>14</v>
       </c>
       <c r="T54" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>9.1842105263157894</v>
       </c>
       <c r="U54" s="12">
@@ -6950,10 +7098,13 @@
       </c>
       <c r="AE54" s="12"/>
       <c r="AF54" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>73.2</v>
       </c>
-      <c r="AG54" s="12"/>
+      <c r="AG54" s="12">
+        <f t="shared" si="5"/>
+        <v>15.200000000000001</v>
+      </c>
       <c r="AH54" s="12"/>
       <c r="AI54" s="12"/>
       <c r="AJ54" s="12"/>
@@ -6999,7 +7150,7 @@
         <v>43</v>
       </c>
       <c r="L55" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-43</v>
       </c>
       <c r="M55" s="12"/>
@@ -7008,22 +7159,22 @@
         <v>20</v>
       </c>
       <c r="P55" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Q55" s="14">
         <v>16</v>
       </c>
       <c r="R55" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="S55" s="12" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T55" s="12" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U55" s="12">
@@ -7060,10 +7211,13 @@
         <v>101</v>
       </c>
       <c r="AF55" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.28</v>
       </c>
-      <c r="AG55" s="12"/>
+      <c r="AG55" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="AH55" s="12"/>
       <c r="AI55" s="12"/>
       <c r="AJ55" s="12"/>
@@ -7113,7 +7267,7 @@
         <v>327.10000000000002</v>
       </c>
       <c r="L56" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.6689999999999827</v>
       </c>
       <c r="M56" s="12"/>
@@ -7122,7 +7276,7 @@
         <v>305</v>
       </c>
       <c r="P56" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>65.753799999999998</v>
       </c>
       <c r="Q56" s="14">
@@ -7130,15 +7284,15 @@
         <v>384.5394</v>
       </c>
       <c r="R56" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>385</v>
       </c>
       <c r="S56" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>13.007004918346924</v>
       </c>
       <c r="T56" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>7.151830008303703</v>
       </c>
       <c r="U56" s="12">
@@ -7173,10 +7327,13 @@
       </c>
       <c r="AE56" s="12"/>
       <c r="AF56" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>385</v>
       </c>
-      <c r="AG56" s="12"/>
+      <c r="AG56" s="12">
+        <f t="shared" si="5"/>
+        <v>65.753799999999998</v>
+      </c>
       <c r="AH56" s="12"/>
       <c r="AI56" s="12"/>
       <c r="AJ56" s="12"/>
@@ -7224,7 +7381,7 @@
         <v>232</v>
       </c>
       <c r="L57" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-245</v>
       </c>
       <c r="M57" s="12"/>
@@ -7233,20 +7390,20 @@
         <v>0</v>
       </c>
       <c r="P57" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-2.6</v>
       </c>
       <c r="Q57" s="14"/>
       <c r="R57" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S57" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-43.846153846153847</v>
       </c>
       <c r="T57" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-43.846153846153847</v>
       </c>
       <c r="U57" s="12">
@@ -7283,10 +7440,13 @@
         <v>47</v>
       </c>
       <c r="AF57" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AG57" s="12"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AG57" s="12">
+        <f t="shared" si="5"/>
+        <v>-1.04</v>
+      </c>
       <c r="AH57" s="12"/>
       <c r="AI57" s="12"/>
       <c r="AJ57" s="12"/>
@@ -7326,7 +7486,7 @@
         <v>20</v>
       </c>
       <c r="L58" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-20</v>
       </c>
       <c r="M58" s="6"/>
@@ -7335,20 +7495,20 @@
         <v>0</v>
       </c>
       <c r="P58" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Q58" s="8"/>
       <c r="R58" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S58" s="12" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T58" s="6" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U58" s="6">
@@ -7385,10 +7545,13 @@
         <v>105</v>
       </c>
       <c r="AF58" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AG58" s="12"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AG58" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="AH58" s="12"/>
       <c r="AI58" s="12"/>
       <c r="AJ58" s="12"/>
@@ -7438,7 +7601,7 @@
         <v>66.5</v>
       </c>
       <c r="L59" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-16.789000000000001</v>
       </c>
       <c r="M59" s="12"/>
@@ -7447,23 +7610,23 @@
         <v>73</v>
       </c>
       <c r="P59" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>9.9421999999999997</v>
       </c>
       <c r="Q59" s="14">
-        <f t="shared" ref="Q59" si="17">14*P59-O59-F59</f>
+        <f t="shared" ref="Q59" si="18">14*P59-O59-F59</f>
         <v>22.892799999999994</v>
       </c>
       <c r="R59" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>23</v>
       </c>
       <c r="S59" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>14.010782321820122</v>
       </c>
       <c r="T59" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>11.697411035786848</v>
       </c>
       <c r="U59" s="12">
@@ -7498,10 +7661,13 @@
       </c>
       <c r="AE59" s="12"/>
       <c r="AF59" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>23</v>
       </c>
-      <c r="AG59" s="12"/>
+      <c r="AG59" s="12">
+        <f t="shared" si="5"/>
+        <v>9.9421999999999997</v>
+      </c>
       <c r="AH59" s="12"/>
       <c r="AI59" s="12"/>
       <c r="AJ59" s="12"/>
@@ -7551,7 +7717,7 @@
         <v>80</v>
       </c>
       <c r="L60" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-32</v>
       </c>
       <c r="M60" s="12"/>
@@ -7560,7 +7726,7 @@
         <v>0</v>
       </c>
       <c r="P60" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>9.6</v>
       </c>
       <c r="Q60" s="14">
@@ -7568,15 +7734,15 @@
         <v>53.199999999999989</v>
       </c>
       <c r="R60" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>53</v>
       </c>
       <c r="S60" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>11.979166666666668</v>
       </c>
       <c r="T60" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>6.4583333333333339</v>
       </c>
       <c r="U60" s="12">
@@ -7611,10 +7777,13 @@
       </c>
       <c r="AE60" s="12"/>
       <c r="AF60" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>31.799999999999997</v>
       </c>
-      <c r="AG60" s="12"/>
+      <c r="AG60" s="12">
+        <f t="shared" si="5"/>
+        <v>5.76</v>
+      </c>
       <c r="AH60" s="12"/>
       <c r="AI60" s="12"/>
       <c r="AJ60" s="12"/>
@@ -7660,7 +7829,7 @@
         <v>16</v>
       </c>
       <c r="L61" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="M61" s="6"/>
@@ -7669,20 +7838,20 @@
         <v>0</v>
       </c>
       <c r="P61" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.2</v>
       </c>
       <c r="Q61" s="8"/>
       <c r="R61" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S61" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>37.5</v>
       </c>
       <c r="T61" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>37.5</v>
       </c>
       <c r="U61" s="6">
@@ -7719,10 +7888,13 @@
         <v>61</v>
       </c>
       <c r="AF61" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AG61" s="12"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AG61" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="AH61" s="12"/>
       <c r="AI61" s="12"/>
       <c r="AJ61" s="12"/>
@@ -7772,7 +7944,7 @@
         <v>311</v>
       </c>
       <c r="L62" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-105</v>
       </c>
       <c r="M62" s="12"/>
@@ -7781,7 +7953,7 @@
         <v>87</v>
       </c>
       <c r="P62" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>41.2</v>
       </c>
       <c r="Q62" s="14">
@@ -7789,15 +7961,15 @@
         <v>238.60000000000002</v>
       </c>
       <c r="R62" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>239</v>
       </c>
       <c r="S62" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>13.009708737864077</v>
       </c>
       <c r="T62" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>7.2087378640776691</v>
       </c>
       <c r="U62" s="12">
@@ -7834,10 +8006,13 @@
         <v>42</v>
       </c>
       <c r="AF62" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>59.75</v>
       </c>
-      <c r="AG62" s="12"/>
+      <c r="AG62" s="12">
+        <f t="shared" si="5"/>
+        <v>10.3</v>
+      </c>
       <c r="AH62" s="12"/>
       <c r="AI62" s="12"/>
       <c r="AJ62" s="12"/>
@@ -7887,7 +8062,7 @@
         <v>22</v>
       </c>
       <c r="L63" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-4.097999999999999</v>
       </c>
       <c r="M63" s="12"/>
@@ -7896,23 +8071,23 @@
         <v>44</v>
       </c>
       <c r="P63" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.5804</v>
       </c>
       <c r="Q63" s="14">
-        <f t="shared" ref="Q63:Q71" si="18">14*P63-O63-F63</f>
+        <f t="shared" ref="Q63:Q71" si="19">14*P63-O63-F63</f>
         <v>5.0695999999999986</v>
       </c>
       <c r="R63" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="S63" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>13.980560831192046</v>
       </c>
       <c r="T63" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>12.584068819126355</v>
       </c>
       <c r="U63" s="12">
@@ -7947,10 +8122,13 @@
       </c>
       <c r="AE63" s="12"/>
       <c r="AF63" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="AG63" s="12"/>
+      <c r="AG63" s="12">
+        <f t="shared" si="5"/>
+        <v>3.5804</v>
+      </c>
       <c r="AH63" s="12"/>
       <c r="AI63" s="12"/>
       <c r="AJ63" s="12"/>
@@ -7998,7 +8176,7 @@
         <v>162</v>
       </c>
       <c r="L64" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-88</v>
       </c>
       <c r="M64" s="12"/>
@@ -8007,22 +8185,22 @@
         <v>205</v>
       </c>
       <c r="P64" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>14.8</v>
       </c>
       <c r="Q64" s="14">
         <v>16</v>
       </c>
       <c r="R64" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="S64" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>14.864864864864865</v>
       </c>
       <c r="T64" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>13.783783783783782</v>
       </c>
       <c r="U64" s="12">
@@ -8059,10 +8237,13 @@
         <v>112</v>
       </c>
       <c r="AF64" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.32</v>
       </c>
-      <c r="AG64" s="12"/>
+      <c r="AG64" s="12">
+        <f t="shared" si="5"/>
+        <v>3.9960000000000004</v>
+      </c>
       <c r="AH64" s="12"/>
       <c r="AI64" s="12"/>
       <c r="AJ64" s="12"/>
@@ -8112,7 +8293,7 @@
         <v>212</v>
       </c>
       <c r="L65" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-165</v>
       </c>
       <c r="M65" s="12"/>
@@ -8121,20 +8302,20 @@
         <v>285</v>
       </c>
       <c r="P65" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>9.4</v>
       </c>
       <c r="Q65" s="14"/>
       <c r="R65" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S65" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>41.063829787234042</v>
       </c>
       <c r="T65" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>41.063829787234042</v>
       </c>
       <c r="U65" s="12">
@@ -8169,10 +8350,13 @@
       </c>
       <c r="AE65" s="12"/>
       <c r="AF65" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AG65" s="12"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AG65" s="12">
+        <f t="shared" si="5"/>
+        <v>2.82</v>
+      </c>
       <c r="AH65" s="12"/>
       <c r="AI65" s="12"/>
       <c r="AJ65" s="12"/>
@@ -8222,7 +8406,7 @@
         <v>1840</v>
       </c>
       <c r="L66" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-217</v>
       </c>
       <c r="M66" s="12"/>
@@ -8231,7 +8415,7 @@
         <v>117</v>
       </c>
       <c r="P66" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>324.60000000000002</v>
       </c>
       <c r="Q66" s="14">
@@ -8239,15 +8423,15 @@
         <v>1901.2000000000003</v>
       </c>
       <c r="R66" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1901</v>
       </c>
       <c r="S66" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>6.9993838570548359</v>
       </c>
       <c r="T66" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1.1429451632778804</v>
       </c>
       <c r="U66" s="12">
@@ -8282,10 +8466,13 @@
       </c>
       <c r="AE66" s="12"/>
       <c r="AF66" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>779.41</v>
       </c>
-      <c r="AG66" s="12"/>
+      <c r="AG66" s="12">
+        <f t="shared" si="5"/>
+        <v>133.08600000000001</v>
+      </c>
       <c r="AH66" s="12"/>
       <c r="AI66" s="12"/>
       <c r="AJ66" s="12"/>
@@ -8335,7 +8522,7 @@
         <v>250.6</v>
       </c>
       <c r="L67" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>10.070000000000022</v>
       </c>
       <c r="M67" s="12"/>
@@ -8344,23 +8531,23 @@
         <v>342</v>
       </c>
       <c r="P67" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>52.134</v>
       </c>
       <c r="Q67" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>161.75099999999998</v>
       </c>
       <c r="R67" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>162</v>
       </c>
       <c r="S67" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>14.004776153757625</v>
       </c>
       <c r="T67" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>10.897399010242836</v>
       </c>
       <c r="U67" s="12">
@@ -8395,10 +8582,13 @@
       </c>
       <c r="AE67" s="12"/>
       <c r="AF67" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>162</v>
       </c>
-      <c r="AG67" s="12"/>
+      <c r="AG67" s="12">
+        <f t="shared" si="5"/>
+        <v>52.134</v>
+      </c>
       <c r="AH67" s="12"/>
       <c r="AI67" s="12"/>
       <c r="AJ67" s="12"/>
@@ -8448,7 +8638,7 @@
         <v>420</v>
       </c>
       <c r="L68" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-275</v>
       </c>
       <c r="M68" s="12"/>
@@ -8457,20 +8647,20 @@
         <v>499</v>
       </c>
       <c r="P68" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>29</v>
       </c>
       <c r="Q68" s="14"/>
       <c r="R68" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S68" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>20.758620689655171</v>
       </c>
       <c r="T68" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>20.758620689655171</v>
       </c>
       <c r="U68" s="12">
@@ -8505,10 +8695,13 @@
       </c>
       <c r="AE68" s="12"/>
       <c r="AF68" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AG68" s="12"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AG68" s="12">
+        <f t="shared" si="5"/>
+        <v>10.149999999999999</v>
+      </c>
       <c r="AH68" s="12"/>
       <c r="AI68" s="12"/>
       <c r="AJ68" s="12"/>
@@ -8558,7 +8751,7 @@
         <v>41</v>
       </c>
       <c r="L69" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-34.716000000000001</v>
       </c>
       <c r="M69" s="12"/>
@@ -8567,20 +8760,20 @@
         <v>56</v>
       </c>
       <c r="P69" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1.2567999999999999</v>
       </c>
       <c r="Q69" s="14"/>
       <c r="R69" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S69" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>44.563176320814769</v>
       </c>
       <c r="T69" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>44.563176320814769</v>
       </c>
       <c r="U69" s="12">
@@ -8615,10 +8808,13 @@
       </c>
       <c r="AE69" s="12"/>
       <c r="AF69" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AG69" s="12"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AG69" s="12">
+        <f t="shared" si="5"/>
+        <v>1.2567999999999999</v>
+      </c>
       <c r="AH69" s="12"/>
       <c r="AI69" s="12"/>
       <c r="AJ69" s="12"/>
@@ -8668,7 +8864,7 @@
         <v>1178</v>
       </c>
       <c r="L70" s="12">
-        <f t="shared" ref="L70:L101" si="19">E70-K70</f>
+        <f t="shared" ref="L70:L101" si="20">E70-K70</f>
         <v>-176</v>
       </c>
       <c r="M70" s="12"/>
@@ -8677,7 +8873,7 @@
         <v>937</v>
       </c>
       <c r="P70" s="12">
-        <f t="shared" ref="P70:P101" si="20">E70/5</f>
+        <f t="shared" ref="P70:P101" si="21">E70/5</f>
         <v>200.4</v>
       </c>
       <c r="Q70" s="14">
@@ -8685,15 +8881,15 @@
         <v>1293.2000000000003</v>
       </c>
       <c r="R70" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1293</v>
       </c>
       <c r="S70" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>12.999001996007983</v>
       </c>
       <c r="T70" s="12">
-        <f t="shared" ref="T70:T101" si="21">(F70+O70)/P70</f>
+        <f t="shared" ref="T70:T101" si="22">(F70+O70)/P70</f>
         <v>6.5469061876247503</v>
       </c>
       <c r="U70" s="12">
@@ -8728,10 +8924,13 @@
       </c>
       <c r="AE70" s="12"/>
       <c r="AF70" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>530.13</v>
       </c>
-      <c r="AG70" s="12"/>
+      <c r="AG70" s="12">
+        <f t="shared" si="5"/>
+        <v>82.164000000000001</v>
+      </c>
       <c r="AH70" s="12"/>
       <c r="AI70" s="12"/>
       <c r="AJ70" s="12"/>
@@ -8781,7 +8980,7 @@
         <v>135.6</v>
       </c>
       <c r="L71" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-48.320999999999998</v>
       </c>
       <c r="M71" s="12"/>
@@ -8790,23 +8989,23 @@
         <v>0</v>
       </c>
       <c r="P71" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>17.4558</v>
       </c>
       <c r="Q71" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>106.4442</v>
       </c>
       <c r="R71" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>106</v>
       </c>
       <c r="S71" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>13.974552870679087</v>
       </c>
       <c r="T71" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>7.90207266352731</v>
       </c>
       <c r="U71" s="12">
@@ -8841,10 +9040,13 @@
       </c>
       <c r="AE71" s="12"/>
       <c r="AF71" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>106</v>
       </c>
-      <c r="AG71" s="12"/>
+      <c r="AG71" s="12">
+        <f t="shared" ref="AG71:AG111" si="23">P71*G71</f>
+        <v>17.4558</v>
+      </c>
       <c r="AH71" s="12"/>
       <c r="AI71" s="12"/>
       <c r="AJ71" s="12"/>
@@ -8894,7 +9096,7 @@
         <v>294</v>
       </c>
       <c r="L72" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-20</v>
       </c>
       <c r="M72" s="12"/>
@@ -8903,7 +9105,7 @@
         <v>7</v>
       </c>
       <c r="P72" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>54.8</v>
       </c>
       <c r="Q72" s="14">
@@ -8911,15 +9113,15 @@
         <v>327</v>
       </c>
       <c r="R72" s="14">
-        <f t="shared" ref="R72:R111" si="22">ROUND(Q72,0)</f>
+        <f t="shared" ref="R72:R111" si="24">ROUND(Q72,0)</f>
         <v>327</v>
       </c>
       <c r="S72" s="12">
-        <f t="shared" ref="S72:S111" si="23">(F72+O72+R72)/P72</f>
+        <f t="shared" ref="S72:S111" si="25">(F72+O72+R72)/P72</f>
         <v>10</v>
       </c>
       <c r="T72" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>4.0328467153284677</v>
       </c>
       <c r="U72" s="12">
@@ -8954,10 +9156,13 @@
       </c>
       <c r="AE72" s="12"/>
       <c r="AF72" s="12">
-        <f t="shared" ref="AF72:AF111" si="24">G72*R72</f>
+        <f t="shared" ref="AF72:AF111" si="26">G72*R72</f>
         <v>98.1</v>
       </c>
-      <c r="AG72" s="12"/>
+      <c r="AG72" s="12">
+        <f t="shared" si="23"/>
+        <v>16.439999999999998</v>
+      </c>
       <c r="AH72" s="12"/>
       <c r="AI72" s="12"/>
       <c r="AJ72" s="12"/>
@@ -9007,7 +9212,7 @@
         <v>289</v>
       </c>
       <c r="L73" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-24</v>
       </c>
       <c r="M73" s="12"/>
@@ -9016,7 +9221,7 @@
         <v>129</v>
       </c>
       <c r="P73" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>53</v>
       </c>
       <c r="Q73" s="14">
@@ -9024,15 +9229,15 @@
         <v>299</v>
       </c>
       <c r="R73" s="14">
+        <f t="shared" si="24"/>
+        <v>299</v>
+      </c>
+      <c r="S73" s="12">
+        <f t="shared" si="25"/>
+        <v>13</v>
+      </c>
+      <c r="T73" s="12">
         <f t="shared" si="22"/>
-        <v>299</v>
-      </c>
-      <c r="S73" s="12">
-        <f t="shared" si="23"/>
-        <v>13</v>
-      </c>
-      <c r="T73" s="12">
-        <f t="shared" si="21"/>
         <v>7.3584905660377355</v>
       </c>
       <c r="U73" s="12">
@@ -9067,10 +9272,13 @@
       </c>
       <c r="AE73" s="12"/>
       <c r="AF73" s="12">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>53.82</v>
       </c>
-      <c r="AG73" s="12"/>
+      <c r="AG73" s="12">
+        <f t="shared" si="23"/>
+        <v>9.5399999999999991</v>
+      </c>
       <c r="AH73" s="12"/>
       <c r="AI73" s="12"/>
       <c r="AJ73" s="12"/>
@@ -9110,7 +9318,7 @@
         <v>5</v>
       </c>
       <c r="L74" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-5</v>
       </c>
       <c r="M74" s="6"/>
@@ -9119,20 +9327,20 @@
         <v>0</v>
       </c>
       <c r="P74" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="Q74" s="8"/>
       <c r="R74" s="14">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S74" s="12" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T74" s="6" t="e">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="S74" s="12" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T74" s="6" t="e">
-        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U74" s="6">
@@ -9169,10 +9377,13 @@
         <v>105</v>
       </c>
       <c r="AF74" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AG74" s="12"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AG74" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="AH74" s="12"/>
       <c r="AI74" s="12"/>
       <c r="AJ74" s="12"/>
@@ -9223,7 +9434,7 @@
         <v>1030</v>
       </c>
       <c r="L75" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-171</v>
       </c>
       <c r="M75" s="12"/>
@@ -9232,7 +9443,7 @@
         <v>956</v>
       </c>
       <c r="P75" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>171.8</v>
       </c>
       <c r="Q75" s="14">
@@ -9240,15 +9451,15 @@
         <v>1058.4000000000001</v>
       </c>
       <c r="R75" s="14">
+        <f t="shared" si="24"/>
+        <v>1058</v>
+      </c>
+      <c r="S75" s="12">
+        <f t="shared" si="25"/>
+        <v>12.997671711292199</v>
+      </c>
+      <c r="T75" s="12">
         <f t="shared" si="22"/>
-        <v>1058</v>
-      </c>
-      <c r="S75" s="12">
-        <f t="shared" si="23"/>
-        <v>12.997671711292199</v>
-      </c>
-      <c r="T75" s="12">
-        <f t="shared" si="21"/>
         <v>6.839348079161816</v>
       </c>
       <c r="U75" s="12">
@@ -9283,10 +9494,13 @@
       </c>
       <c r="AE75" s="12"/>
       <c r="AF75" s="12">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>370.29999999999995</v>
       </c>
-      <c r="AG75" s="12"/>
+      <c r="AG75" s="12">
+        <f t="shared" si="23"/>
+        <v>60.13</v>
+      </c>
       <c r="AH75" s="12"/>
       <c r="AI75" s="12"/>
       <c r="AJ75" s="12"/>
@@ -9324,7 +9538,7 @@
       <c r="J76" s="6"/>
       <c r="K76" s="6"/>
       <c r="L76" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="M76" s="6"/>
@@ -9333,20 +9547,20 @@
         <v>0</v>
       </c>
       <c r="P76" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="Q76" s="8"/>
       <c r="R76" s="14">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S76" s="12" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T76" s="6" t="e">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="S76" s="12" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T76" s="6" t="e">
-        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U76" s="6">
@@ -9383,10 +9597,13 @@
         <v>105</v>
       </c>
       <c r="AF76" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AG76" s="12"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AG76" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="AH76" s="12"/>
       <c r="AI76" s="12"/>
       <c r="AJ76" s="12"/>
@@ -9436,7 +9653,7 @@
         <v>187.5</v>
       </c>
       <c r="L77" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4.9050000000000011</v>
       </c>
       <c r="M77" s="12"/>
@@ -9445,23 +9662,23 @@
         <v>49</v>
       </c>
       <c r="P77" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>38.481000000000002</v>
       </c>
       <c r="Q77" s="14">
-        <f t="shared" ref="Q77" si="25">14*P77-O77-F77</f>
+        <f t="shared" ref="Q77" si="27">14*P77-O77-F77</f>
         <v>202.24900000000002</v>
       </c>
       <c r="R77" s="14">
+        <f t="shared" si="24"/>
+        <v>202</v>
+      </c>
+      <c r="S77" s="12">
+        <f t="shared" si="25"/>
+        <v>13.99352927418726</v>
+      </c>
+      <c r="T77" s="12">
         <f t="shared" si="22"/>
-        <v>202</v>
-      </c>
-      <c r="S77" s="12">
-        <f t="shared" si="23"/>
-        <v>13.99352927418726</v>
-      </c>
-      <c r="T77" s="12">
-        <f t="shared" si="21"/>
         <v>8.7441854421662644</v>
       </c>
       <c r="U77" s="12">
@@ -9496,10 +9713,13 @@
       </c>
       <c r="AE77" s="12"/>
       <c r="AF77" s="12">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>202</v>
       </c>
-      <c r="AG77" s="12"/>
+      <c r="AG77" s="12">
+        <f t="shared" si="23"/>
+        <v>38.481000000000002</v>
+      </c>
       <c r="AH77" s="12"/>
       <c r="AI77" s="12"/>
       <c r="AJ77" s="12"/>
@@ -9549,7 +9769,7 @@
         <v>324.89999999999998</v>
       </c>
       <c r="L78" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>24.073000000000036</v>
       </c>
       <c r="M78" s="12"/>
@@ -9558,23 +9778,23 @@
         <v>249</v>
       </c>
       <c r="P78" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>69.794600000000003</v>
       </c>
       <c r="Q78" s="14">
-        <f t="shared" ref="Q78:Q79" si="26">13*P78-O78-F78</f>
+        <f t="shared" ref="Q78:Q79" si="28">13*P78-O78-F78</f>
         <v>409.76679999999999</v>
       </c>
       <c r="R78" s="14">
+        <f t="shared" si="24"/>
+        <v>410</v>
+      </c>
+      <c r="S78" s="12">
+        <f t="shared" si="25"/>
+        <v>13.003341232702816</v>
+      </c>
+      <c r="T78" s="12">
         <f t="shared" si="22"/>
-        <v>410</v>
-      </c>
-      <c r="S78" s="12">
-        <f t="shared" si="23"/>
-        <v>13.003341232702816</v>
-      </c>
-      <c r="T78" s="12">
-        <f t="shared" si="21"/>
         <v>7.1289612663443869</v>
       </c>
       <c r="U78" s="12">
@@ -9609,10 +9829,13 @@
       </c>
       <c r="AE78" s="12"/>
       <c r="AF78" s="12">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>410</v>
       </c>
-      <c r="AG78" s="12"/>
+      <c r="AG78" s="12">
+        <f t="shared" si="23"/>
+        <v>69.794600000000003</v>
+      </c>
       <c r="AH78" s="12"/>
       <c r="AI78" s="12"/>
       <c r="AJ78" s="12"/>
@@ -9662,7 +9885,7 @@
         <v>946</v>
       </c>
       <c r="L79" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-41</v>
       </c>
       <c r="M79" s="12"/>
@@ -9671,23 +9894,23 @@
         <v>797</v>
       </c>
       <c r="P79" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>181</v>
       </c>
       <c r="Q79" s="14">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1121</v>
       </c>
       <c r="R79" s="14">
+        <f t="shared" si="24"/>
+        <v>1121</v>
+      </c>
+      <c r="S79" s="12">
+        <f t="shared" si="25"/>
+        <v>13</v>
+      </c>
+      <c r="T79" s="12">
         <f t="shared" si="22"/>
-        <v>1121</v>
-      </c>
-      <c r="S79" s="12">
-        <f t="shared" si="23"/>
-        <v>13</v>
-      </c>
-      <c r="T79" s="12">
-        <f t="shared" si="21"/>
         <v>6.806629834254144</v>
       </c>
       <c r="U79" s="12">
@@ -9722,10 +9945,13 @@
       </c>
       <c r="AE79" s="12"/>
       <c r="AF79" s="12">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>392.34999999999997</v>
       </c>
-      <c r="AG79" s="12"/>
+      <c r="AG79" s="12">
+        <f t="shared" si="23"/>
+        <v>63.349999999999994</v>
+      </c>
       <c r="AH79" s="12"/>
       <c r="AI79" s="12"/>
       <c r="AJ79" s="12"/>
@@ -9771,7 +9997,7 @@
         <v>127</v>
       </c>
       <c r="L80" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-109</v>
       </c>
       <c r="M80" s="6"/>
@@ -9780,20 +10006,20 @@
         <v>0</v>
       </c>
       <c r="P80" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>3.6</v>
       </c>
       <c r="Q80" s="8"/>
       <c r="R80" s="14">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S80" s="12">
+        <f t="shared" si="25"/>
+        <v>30.555555555555554</v>
+      </c>
+      <c r="T80" s="6">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="S80" s="12">
-        <f t="shared" si="23"/>
-        <v>30.555555555555554</v>
-      </c>
-      <c r="T80" s="6">
-        <f t="shared" si="21"/>
         <v>30.555555555555554</v>
       </c>
       <c r="U80" s="6">
@@ -9830,10 +10056,13 @@
         <v>37</v>
       </c>
       <c r="AF80" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AG80" s="12"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AG80" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="AH80" s="12"/>
       <c r="AI80" s="12"/>
       <c r="AJ80" s="12"/>
@@ -9883,7 +10112,7 @@
         <v>354</v>
       </c>
       <c r="L81" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-158</v>
       </c>
       <c r="M81" s="12"/>
@@ -9892,7 +10121,7 @@
         <v>152</v>
       </c>
       <c r="P81" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>39.200000000000003</v>
       </c>
       <c r="Q81" s="14">
@@ -9900,15 +10129,15 @@
         <v>222</v>
       </c>
       <c r="R81" s="14">
+        <f t="shared" si="24"/>
+        <v>222</v>
+      </c>
+      <c r="S81" s="12">
+        <f t="shared" si="25"/>
+        <v>10</v>
+      </c>
+      <c r="T81" s="12">
         <f t="shared" si="22"/>
-        <v>222</v>
-      </c>
-      <c r="S81" s="12">
-        <f t="shared" si="23"/>
-        <v>10</v>
-      </c>
-      <c r="T81" s="12">
-        <f t="shared" si="21"/>
         <v>4.3367346938775508</v>
       </c>
       <c r="U81" s="12">
@@ -9943,10 +10172,13 @@
       </c>
       <c r="AE81" s="12"/>
       <c r="AF81" s="12">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>66.599999999999994</v>
       </c>
-      <c r="AG81" s="12"/>
+      <c r="AG81" s="12">
+        <f t="shared" si="23"/>
+        <v>11.76</v>
+      </c>
       <c r="AH81" s="12"/>
       <c r="AI81" s="12"/>
       <c r="AJ81" s="12"/>
@@ -9996,7 +10228,7 @@
         <v>123</v>
       </c>
       <c r="L82" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-97</v>
       </c>
       <c r="M82" s="12"/>
@@ -10005,22 +10237,22 @@
         <v>60</v>
       </c>
       <c r="P82" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5.2</v>
       </c>
       <c r="Q82" s="14">
         <v>16</v>
       </c>
       <c r="R82" s="14">
+        <f t="shared" si="24"/>
+        <v>16</v>
+      </c>
+      <c r="S82" s="12">
+        <f t="shared" si="25"/>
+        <v>22.884615384615383</v>
+      </c>
+      <c r="T82" s="12">
         <f t="shared" si="22"/>
-        <v>16</v>
-      </c>
-      <c r="S82" s="12">
-        <f t="shared" si="23"/>
-        <v>22.884615384615383</v>
-      </c>
-      <c r="T82" s="12">
-        <f t="shared" si="21"/>
         <v>19.807692307692307</v>
       </c>
       <c r="U82" s="12">
@@ -10055,10 +10287,13 @@
       </c>
       <c r="AE82" s="12"/>
       <c r="AF82" s="12">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>4.8</v>
       </c>
-      <c r="AG82" s="12"/>
+      <c r="AG82" s="12">
+        <f t="shared" si="23"/>
+        <v>1.56</v>
+      </c>
       <c r="AH82" s="12"/>
       <c r="AI82" s="12"/>
       <c r="AJ82" s="12"/>
@@ -10108,7 +10343,7 @@
         <v>638</v>
       </c>
       <c r="L83" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-85</v>
       </c>
       <c r="M83" s="12"/>
@@ -10117,7 +10352,7 @@
         <v>619</v>
       </c>
       <c r="P83" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>110.6</v>
       </c>
       <c r="Q83" s="14">
@@ -10125,15 +10360,15 @@
         <v>702.8</v>
       </c>
       <c r="R83" s="14">
+        <f t="shared" si="24"/>
+        <v>703</v>
+      </c>
+      <c r="S83" s="12">
+        <f t="shared" si="25"/>
+        <v>13.001808318264015</v>
+      </c>
+      <c r="T83" s="12">
         <f t="shared" si="22"/>
-        <v>703</v>
-      </c>
-      <c r="S83" s="12">
-        <f t="shared" si="23"/>
-        <v>13.001808318264015</v>
-      </c>
-      <c r="T83" s="12">
-        <f t="shared" si="21"/>
         <v>6.6455696202531653</v>
       </c>
       <c r="U83" s="12">
@@ -10168,10 +10403,13 @@
       </c>
       <c r="AE83" s="12"/>
       <c r="AF83" s="12">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>196.84000000000003</v>
       </c>
-      <c r="AG83" s="12"/>
+      <c r="AG83" s="12">
+        <f t="shared" si="23"/>
+        <v>30.968</v>
+      </c>
       <c r="AH83" s="12"/>
       <c r="AI83" s="12"/>
       <c r="AJ83" s="12"/>
@@ -10221,7 +10459,7 @@
         <v>691</v>
       </c>
       <c r="L84" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-31</v>
       </c>
       <c r="M84" s="12"/>
@@ -10230,7 +10468,7 @@
         <v>465</v>
       </c>
       <c r="P84" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>132</v>
       </c>
       <c r="Q84" s="14">
@@ -10238,15 +10476,15 @@
         <v>780</v>
       </c>
       <c r="R84" s="14">
+        <f t="shared" si="24"/>
+        <v>780</v>
+      </c>
+      <c r="S84" s="12">
+        <f t="shared" si="25"/>
+        <v>11</v>
+      </c>
+      <c r="T84" s="12">
         <f t="shared" si="22"/>
-        <v>780</v>
-      </c>
-      <c r="S84" s="12">
-        <f t="shared" si="23"/>
-        <v>11</v>
-      </c>
-      <c r="T84" s="12">
-        <f t="shared" si="21"/>
         <v>5.0909090909090908</v>
       </c>
       <c r="U84" s="12">
@@ -10281,10 +10519,13 @@
       </c>
       <c r="AE84" s="12"/>
       <c r="AF84" s="12">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>218.40000000000003</v>
       </c>
-      <c r="AG84" s="12"/>
+      <c r="AG84" s="12">
+        <f t="shared" si="23"/>
+        <v>36.96</v>
+      </c>
       <c r="AH84" s="12"/>
       <c r="AI84" s="12"/>
       <c r="AJ84" s="12"/>
@@ -10330,7 +10571,7 @@
         <v>18</v>
       </c>
       <c r="L85" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-16</v>
       </c>
       <c r="M85" s="6"/>
@@ -10339,20 +10580,20 @@
         <v>0</v>
       </c>
       <c r="P85" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.4</v>
       </c>
       <c r="Q85" s="8"/>
       <c r="R85" s="14">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S85" s="12">
+        <f t="shared" si="25"/>
+        <v>350</v>
+      </c>
+      <c r="T85" s="6">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="S85" s="12">
-        <f t="shared" si="23"/>
-        <v>350</v>
-      </c>
-      <c r="T85" s="6">
-        <f t="shared" si="21"/>
         <v>350</v>
       </c>
       <c r="U85" s="6">
@@ -10389,10 +10630,13 @@
         <v>37</v>
       </c>
       <c r="AF85" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AG85" s="12"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AG85" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="AH85" s="12"/>
       <c r="AI85" s="12"/>
       <c r="AJ85" s="12"/>
@@ -10442,7 +10686,7 @@
         <v>590</v>
       </c>
       <c r="L86" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-74</v>
       </c>
       <c r="M86" s="12"/>
@@ -10451,7 +10695,7 @@
         <v>281</v>
       </c>
       <c r="P86" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>103.2</v>
       </c>
       <c r="Q86" s="14">
@@ -10459,15 +10703,15 @@
         <v>637.20000000000005</v>
       </c>
       <c r="R86" s="14">
+        <f t="shared" si="24"/>
+        <v>637</v>
+      </c>
+      <c r="S86" s="12">
+        <f t="shared" si="25"/>
+        <v>10.998062015503876</v>
+      </c>
+      <c r="T86" s="12">
         <f t="shared" si="22"/>
-        <v>637</v>
-      </c>
-      <c r="S86" s="12">
-        <f t="shared" si="23"/>
-        <v>10.998062015503876</v>
-      </c>
-      <c r="T86" s="12">
-        <f t="shared" si="21"/>
         <v>4.8255813953488369</v>
       </c>
       <c r="U86" s="12">
@@ -10502,10 +10746,13 @@
       </c>
       <c r="AE86" s="12"/>
       <c r="AF86" s="12">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>178.36</v>
       </c>
-      <c r="AG86" s="12"/>
+      <c r="AG86" s="12">
+        <f t="shared" si="23"/>
+        <v>28.896000000000004</v>
+      </c>
       <c r="AH86" s="12"/>
       <c r="AI86" s="12"/>
       <c r="AJ86" s="12"/>
@@ -10555,7 +10802,7 @@
         <v>1506</v>
       </c>
       <c r="L87" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-767</v>
       </c>
       <c r="M87" s="12"/>
@@ -10564,23 +10811,23 @@
         <v>962</v>
       </c>
       <c r="P87" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>147.80000000000001</v>
       </c>
       <c r="Q87" s="14">
-        <f t="shared" ref="Q87" si="27">14*P87-O87-F87</f>
+        <f t="shared" ref="Q87" si="29">14*P87-O87-F87</f>
         <v>352.20000000000027</v>
       </c>
       <c r="R87" s="14">
+        <f t="shared" si="24"/>
+        <v>352</v>
+      </c>
+      <c r="S87" s="12">
+        <f t="shared" si="25"/>
+        <v>13.998646820027062</v>
+      </c>
+      <c r="T87" s="12">
         <f t="shared" si="22"/>
-        <v>352</v>
-      </c>
-      <c r="S87" s="12">
-        <f t="shared" si="23"/>
-        <v>13.998646820027062</v>
-      </c>
-      <c r="T87" s="12">
-        <f t="shared" si="21"/>
         <v>11.617050067658997</v>
       </c>
       <c r="U87" s="12">
@@ -10615,10 +10862,13 @@
       </c>
       <c r="AE87" s="12"/>
       <c r="AF87" s="12">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>140.80000000000001</v>
       </c>
-      <c r="AG87" s="12"/>
+      <c r="AG87" s="12">
+        <f t="shared" si="23"/>
+        <v>59.120000000000005</v>
+      </c>
       <c r="AH87" s="12"/>
       <c r="AI87" s="12"/>
       <c r="AJ87" s="12"/>
@@ -10664,27 +10914,27 @@
         <v>9</v>
       </c>
       <c r="L88" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-8</v>
       </c>
       <c r="M88" s="6"/>
       <c r="N88" s="6"/>
       <c r="O88" s="6"/>
       <c r="P88" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.2</v>
       </c>
       <c r="Q88" s="8"/>
       <c r="R88" s="14">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S88" s="12">
+        <f t="shared" si="25"/>
+        <v>-5</v>
+      </c>
+      <c r="T88" s="6">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="S88" s="12">
-        <f t="shared" si="23"/>
-        <v>-5</v>
-      </c>
-      <c r="T88" s="6">
-        <f t="shared" si="21"/>
         <v>-5</v>
       </c>
       <c r="U88" s="6">
@@ -10719,10 +10969,13 @@
       </c>
       <c r="AE88" s="6"/>
       <c r="AF88" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AG88" s="12"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AG88" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="AH88" s="12"/>
       <c r="AI88" s="12"/>
       <c r="AJ88" s="12"/>
@@ -10772,7 +11025,7 @@
         <v>39</v>
       </c>
       <c r="L89" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-18.829000000000001</v>
       </c>
       <c r="M89" s="12"/>
@@ -10781,20 +11034,20 @@
         <v>0</v>
       </c>
       <c r="P89" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>4.0342000000000002</v>
       </c>
       <c r="Q89" s="14"/>
       <c r="R89" s="14">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S89" s="12">
+        <f t="shared" si="25"/>
+        <v>30.659362451043577</v>
+      </c>
+      <c r="T89" s="12">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="S89" s="12">
-        <f t="shared" si="23"/>
-        <v>30.659362451043577</v>
-      </c>
-      <c r="T89" s="12">
-        <f t="shared" si="21"/>
         <v>30.659362451043577</v>
       </c>
       <c r="U89" s="12">
@@ -10831,10 +11084,13 @@
         <v>138</v>
       </c>
       <c r="AF89" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AG89" s="12"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AG89" s="12">
+        <f t="shared" si="23"/>
+        <v>4.0342000000000002</v>
+      </c>
       <c r="AH89" s="12"/>
       <c r="AI89" s="12"/>
       <c r="AJ89" s="12"/>
@@ -10882,7 +11138,7 @@
         <v>120</v>
       </c>
       <c r="L90" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-100</v>
       </c>
       <c r="M90" s="12"/>
@@ -10891,23 +11147,23 @@
         <v>6</v>
       </c>
       <c r="P90" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>4</v>
       </c>
       <c r="Q90" s="14">
-        <f t="shared" ref="Q90" si="28">14*P90-O90-F90</f>
+        <f t="shared" ref="Q90" si="30">14*P90-O90-F90</f>
         <v>25</v>
       </c>
       <c r="R90" s="14">
+        <f t="shared" si="24"/>
+        <v>25</v>
+      </c>
+      <c r="S90" s="12">
+        <f t="shared" si="25"/>
+        <v>14</v>
+      </c>
+      <c r="T90" s="12">
         <f t="shared" si="22"/>
-        <v>25</v>
-      </c>
-      <c r="S90" s="12">
-        <f t="shared" si="23"/>
-        <v>14</v>
-      </c>
-      <c r="T90" s="12">
-        <f t="shared" si="21"/>
         <v>7.75</v>
       </c>
       <c r="U90" s="12">
@@ -10942,10 +11198,13 @@
       </c>
       <c r="AE90" s="12"/>
       <c r="AF90" s="12">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>7.0000000000000009</v>
       </c>
-      <c r="AG90" s="12"/>
+      <c r="AG90" s="12">
+        <f t="shared" si="23"/>
+        <v>1.1200000000000001</v>
+      </c>
       <c r="AH90" s="12"/>
       <c r="AI90" s="12"/>
       <c r="AJ90" s="12"/>
@@ -10989,7 +11248,7 @@
         <v>16</v>
       </c>
       <c r="L91" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-16</v>
       </c>
       <c r="M91" s="6"/>
@@ -10998,20 +11257,20 @@
         <v>0</v>
       </c>
       <c r="P91" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="Q91" s="8"/>
       <c r="R91" s="14">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S91" s="12" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T91" s="6" t="e">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="S91" s="12" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T91" s="6" t="e">
-        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U91" s="6">
@@ -11048,10 +11307,13 @@
         <v>37</v>
       </c>
       <c r="AF91" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AG91" s="12"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AG91" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="AH91" s="12"/>
       <c r="AI91" s="12"/>
       <c r="AJ91" s="12"/>
@@ -11101,7 +11363,7 @@
         <v>543</v>
       </c>
       <c r="L92" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-128</v>
       </c>
       <c r="M92" s="12"/>
@@ -11110,7 +11372,7 @@
         <v>398</v>
       </c>
       <c r="P92" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>83</v>
       </c>
       <c r="Q92" s="14">
@@ -11118,15 +11380,15 @@
         <v>465</v>
       </c>
       <c r="R92" s="14">
+        <f t="shared" si="24"/>
+        <v>465</v>
+      </c>
+      <c r="S92" s="12">
+        <f t="shared" si="25"/>
+        <v>14</v>
+      </c>
+      <c r="T92" s="12">
         <f t="shared" si="22"/>
-        <v>465</v>
-      </c>
-      <c r="S92" s="12">
-        <f t="shared" si="23"/>
-        <v>14</v>
-      </c>
-      <c r="T92" s="12">
-        <f t="shared" si="21"/>
         <v>8.3975903614457827</v>
       </c>
       <c r="U92" s="12">
@@ -11161,10 +11423,13 @@
       </c>
       <c r="AE92" s="12"/>
       <c r="AF92" s="12">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>55.8</v>
       </c>
-      <c r="AG92" s="12"/>
+      <c r="AG92" s="12">
+        <f t="shared" si="23"/>
+        <v>9.9599999999999991</v>
+      </c>
       <c r="AH92" s="12"/>
       <c r="AI92" s="12"/>
       <c r="AJ92" s="12"/>
@@ -11212,7 +11477,7 @@
         <v>75</v>
       </c>
       <c r="L93" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-30</v>
       </c>
       <c r="M93" s="6"/>
@@ -11221,20 +11486,20 @@
         <v>0</v>
       </c>
       <c r="P93" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>9</v>
       </c>
       <c r="Q93" s="8"/>
       <c r="R93" s="14">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S93" s="12">
+        <f t="shared" si="25"/>
+        <v>3.8888888888888888</v>
+      </c>
+      <c r="T93" s="6">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="S93" s="12">
-        <f t="shared" si="23"/>
-        <v>3.8888888888888888</v>
-      </c>
-      <c r="T93" s="6">
-        <f t="shared" si="21"/>
         <v>3.8888888888888888</v>
       </c>
       <c r="U93" s="6">
@@ -11271,10 +11536,13 @@
         <v>61</v>
       </c>
       <c r="AF93" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AG93" s="12"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AG93" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="AH93" s="12"/>
       <c r="AI93" s="12"/>
       <c r="AJ93" s="12"/>
@@ -11326,7 +11594,7 @@
         <v>282</v>
       </c>
       <c r="L94" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-67</v>
       </c>
       <c r="M94" s="12"/>
@@ -11335,23 +11603,23 @@
         <v>248</v>
       </c>
       <c r="P94" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>43</v>
       </c>
       <c r="Q94" s="14">
-        <f t="shared" ref="Q94:Q96" si="29">14*P94-O94-F94</f>
+        <f t="shared" ref="Q94:Q96" si="31">14*P94-O94-F94</f>
         <v>194</v>
       </c>
       <c r="R94" s="14">
+        <f t="shared" si="24"/>
+        <v>194</v>
+      </c>
+      <c r="S94" s="12">
+        <f t="shared" si="25"/>
+        <v>14</v>
+      </c>
+      <c r="T94" s="12">
         <f t="shared" si="22"/>
-        <v>194</v>
-      </c>
-      <c r="S94" s="12">
-        <f t="shared" si="23"/>
-        <v>14</v>
-      </c>
-      <c r="T94" s="12">
-        <f t="shared" si="21"/>
         <v>9.4883720930232567</v>
       </c>
       <c r="U94" s="12">
@@ -11386,10 +11654,13 @@
       </c>
       <c r="AE94" s="12"/>
       <c r="AF94" s="12">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>64.02</v>
       </c>
-      <c r="AG94" s="12"/>
+      <c r="AG94" s="12">
+        <f t="shared" si="23"/>
+        <v>14.190000000000001</v>
+      </c>
       <c r="AH94" s="12"/>
       <c r="AI94" s="12"/>
       <c r="AJ94" s="12"/>
@@ -11439,7 +11710,7 @@
         <v>271</v>
       </c>
       <c r="L95" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-232</v>
       </c>
       <c r="M95" s="12"/>
@@ -11448,7 +11719,7 @@
         <v>0</v>
       </c>
       <c r="P95" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>7.8</v>
       </c>
       <c r="Q95" s="14">
@@ -11456,15 +11727,15 @@
         <v>49.399999999999991</v>
       </c>
       <c r="R95" s="14">
+        <f t="shared" si="24"/>
+        <v>49</v>
+      </c>
+      <c r="S95" s="12">
+        <f t="shared" si="25"/>
+        <v>12.948717948717949</v>
+      </c>
+      <c r="T95" s="12">
         <f t="shared" si="22"/>
-        <v>49</v>
-      </c>
-      <c r="S95" s="12">
-        <f t="shared" si="23"/>
-        <v>12.948717948717949</v>
-      </c>
-      <c r="T95" s="12">
-        <f t="shared" si="21"/>
         <v>6.666666666666667</v>
       </c>
       <c r="U95" s="12">
@@ -11501,10 +11772,13 @@
         <v>144</v>
       </c>
       <c r="AF95" s="12">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>7.35</v>
       </c>
-      <c r="AG95" s="12"/>
+      <c r="AG95" s="12">
+        <f t="shared" si="23"/>
+        <v>1.17</v>
+      </c>
       <c r="AH95" s="12"/>
       <c r="AI95" s="12"/>
       <c r="AJ95" s="12"/>
@@ -11554,7 +11828,7 @@
         <v>121</v>
       </c>
       <c r="L96" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-87</v>
       </c>
       <c r="M96" s="12"/>
@@ -11563,23 +11837,23 @@
         <v>0</v>
       </c>
       <c r="P96" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>6.8</v>
       </c>
       <c r="Q96" s="14">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>39.200000000000003</v>
       </c>
       <c r="R96" s="14">
+        <f t="shared" si="24"/>
+        <v>39</v>
+      </c>
+      <c r="S96" s="12">
+        <f t="shared" si="25"/>
+        <v>13.970588235294118</v>
+      </c>
+      <c r="T96" s="12">
         <f t="shared" si="22"/>
-        <v>39</v>
-      </c>
-      <c r="S96" s="12">
-        <f t="shared" si="23"/>
-        <v>13.970588235294118</v>
-      </c>
-      <c r="T96" s="12">
-        <f t="shared" si="21"/>
         <v>8.2352941176470598</v>
       </c>
       <c r="U96" s="12">
@@ -11616,10 +11890,13 @@
         <v>146</v>
       </c>
       <c r="AF96" s="12">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>10.14</v>
       </c>
-      <c r="AG96" s="12"/>
+      <c r="AG96" s="12">
+        <f t="shared" si="23"/>
+        <v>1.768</v>
+      </c>
       <c r="AH96" s="12"/>
       <c r="AI96" s="12"/>
       <c r="AJ96" s="12"/>
@@ -11669,7 +11946,7 @@
         <v>160</v>
       </c>
       <c r="L97" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-121</v>
       </c>
       <c r="M97" s="12"/>
@@ -11678,7 +11955,7 @@
         <v>0</v>
       </c>
       <c r="P97" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>7.8</v>
       </c>
       <c r="Q97" s="14">
@@ -11686,15 +11963,15 @@
         <v>48.599999999999994</v>
       </c>
       <c r="R97" s="14">
+        <f t="shared" si="24"/>
+        <v>49</v>
+      </c>
+      <c r="S97" s="12">
+        <f t="shared" si="25"/>
+        <v>12.051282051282051</v>
+      </c>
+      <c r="T97" s="12">
         <f t="shared" si="22"/>
-        <v>49</v>
-      </c>
-      <c r="S97" s="12">
-        <f t="shared" si="23"/>
-        <v>12.051282051282051</v>
-      </c>
-      <c r="T97" s="12">
-        <f t="shared" si="21"/>
         <v>5.7692307692307692</v>
       </c>
       <c r="U97" s="12">
@@ -11731,10 +12008,13 @@
         <v>146</v>
       </c>
       <c r="AF97" s="12">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>15.19</v>
       </c>
-      <c r="AG97" s="12"/>
+      <c r="AG97" s="12">
+        <f t="shared" si="23"/>
+        <v>2.4180000000000001</v>
+      </c>
       <c r="AH97" s="12"/>
       <c r="AI97" s="12"/>
       <c r="AJ97" s="12"/>
@@ -11784,7 +12064,7 @@
         <v>318</v>
       </c>
       <c r="L98" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>7</v>
       </c>
       <c r="M98" s="12"/>
@@ -11793,7 +12073,7 @@
         <v>252</v>
       </c>
       <c r="P98" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>65</v>
       </c>
       <c r="Q98" s="14">
@@ -11801,15 +12081,15 @@
         <v>416</v>
       </c>
       <c r="R98" s="14">
+        <f t="shared" si="24"/>
+        <v>416</v>
+      </c>
+      <c r="S98" s="12">
+        <f t="shared" si="25"/>
+        <v>13</v>
+      </c>
+      <c r="T98" s="12">
         <f t="shared" si="22"/>
-        <v>416</v>
-      </c>
-      <c r="S98" s="12">
-        <f t="shared" si="23"/>
-        <v>13</v>
-      </c>
-      <c r="T98" s="12">
-        <f t="shared" si="21"/>
         <v>6.6</v>
       </c>
       <c r="U98" s="12">
@@ -11844,10 +12124,13 @@
       </c>
       <c r="AE98" s="12"/>
       <c r="AF98" s="12">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>166.4</v>
       </c>
-      <c r="AG98" s="12"/>
+      <c r="AG98" s="12">
+        <f t="shared" si="23"/>
+        <v>26</v>
+      </c>
       <c r="AH98" s="12"/>
       <c r="AI98" s="12"/>
       <c r="AJ98" s="12"/>
@@ -11889,7 +12172,7 @@
         <v>289</v>
       </c>
       <c r="L99" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-289</v>
       </c>
       <c r="M99" s="12"/>
@@ -11898,20 +12181,20 @@
         <v>40</v>
       </c>
       <c r="P99" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="Q99" s="14"/>
       <c r="R99" s="14">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S99" s="12" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T99" s="12" t="e">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="S99" s="12" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T99" s="12" t="e">
-        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U99" s="12">
@@ -11948,10 +12231,13 @@
         <v>150</v>
       </c>
       <c r="AF99" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AG99" s="12"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AG99" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="AH99" s="12"/>
       <c r="AI99" s="12"/>
       <c r="AJ99" s="12"/>
@@ -12001,7 +12287,7 @@
         <v>40.299999999999997</v>
       </c>
       <c r="L100" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-38.564999999999998</v>
       </c>
       <c r="M100" s="12"/>
@@ -12010,20 +12296,20 @@
         <v>0</v>
       </c>
       <c r="P100" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.34700000000000003</v>
       </c>
       <c r="Q100" s="14"/>
       <c r="R100" s="14">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S100" s="12">
+        <f t="shared" si="25"/>
+        <v>227.06340057636885</v>
+      </c>
+      <c r="T100" s="12">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="S100" s="12">
-        <f t="shared" si="23"/>
-        <v>227.06340057636885</v>
-      </c>
-      <c r="T100" s="12">
-        <f t="shared" si="21"/>
         <v>227.06340057636885</v>
       </c>
       <c r="U100" s="12">
@@ -12060,10 +12346,13 @@
         <v>152</v>
       </c>
       <c r="AF100" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AG100" s="12"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AG100" s="12">
+        <f t="shared" si="23"/>
+        <v>0.34700000000000003</v>
+      </c>
       <c r="AH100" s="12"/>
       <c r="AI100" s="12"/>
       <c r="AJ100" s="12"/>
@@ -12113,7 +12402,7 @@
         <v>64.98</v>
       </c>
       <c r="L101" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-1.480000000000004</v>
       </c>
       <c r="M101" s="12"/>
@@ -12122,7 +12411,7 @@
         <v>0</v>
       </c>
       <c r="P101" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>12.7</v>
       </c>
       <c r="Q101" s="14">
@@ -12130,15 +12419,15 @@
         <v>81.412999999999997</v>
       </c>
       <c r="R101" s="14">
+        <f t="shared" si="24"/>
+        <v>81</v>
+      </c>
+      <c r="S101" s="12">
+        <f t="shared" si="25"/>
+        <v>8.9674803149606301</v>
+      </c>
+      <c r="T101" s="12">
         <f t="shared" si="22"/>
-        <v>81</v>
-      </c>
-      <c r="S101" s="12">
-        <f t="shared" si="23"/>
-        <v>8.9674803149606301</v>
-      </c>
-      <c r="T101" s="12">
-        <f t="shared" si="21"/>
         <v>2.5895275590551181</v>
       </c>
       <c r="U101" s="12">
@@ -12173,10 +12462,13 @@
       </c>
       <c r="AE101" s="12"/>
       <c r="AF101" s="12">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>81</v>
       </c>
-      <c r="AG101" s="12"/>
+      <c r="AG101" s="12">
+        <f t="shared" si="23"/>
+        <v>12.7</v>
+      </c>
       <c r="AH101" s="12"/>
       <c r="AI101" s="12"/>
       <c r="AJ101" s="12"/>
@@ -12222,7 +12514,7 @@
         <v>39</v>
       </c>
       <c r="L102" s="6">
-        <f t="shared" ref="L102:L111" si="30">E102-K102</f>
+        <f t="shared" ref="L102:L111" si="32">E102-K102</f>
         <v>-17</v>
       </c>
       <c r="M102" s="6"/>
@@ -12231,20 +12523,20 @@
         <v>0</v>
       </c>
       <c r="P102" s="6">
-        <f t="shared" ref="P102:P111" si="31">E102/5</f>
+        <f t="shared" ref="P102:P111" si="33">E102/5</f>
         <v>4.4000000000000004</v>
       </c>
       <c r="Q102" s="8"/>
       <c r="R102" s="14">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="S102" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>36.36363636363636</v>
       </c>
       <c r="T102" s="6">
-        <f t="shared" ref="T102:T111" si="32">(F102+O102)/P102</f>
+        <f t="shared" ref="T102:T111" si="34">(F102+O102)/P102</f>
         <v>36.36363636363636</v>
       </c>
       <c r="U102" s="6">
@@ -12281,10 +12573,13 @@
         <v>155</v>
       </c>
       <c r="AF102" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AG102" s="12"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AG102" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="AH102" s="12"/>
       <c r="AI102" s="12"/>
       <c r="AJ102" s="12"/>
@@ -12332,7 +12627,7 @@
         <v>501</v>
       </c>
       <c r="L103" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>-512</v>
       </c>
       <c r="M103" s="12"/>
@@ -12341,20 +12636,20 @@
         <v>156</v>
       </c>
       <c r="P103" s="12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-2.2000000000000002</v>
       </c>
       <c r="Q103" s="14"/>
       <c r="R103" s="14">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="S103" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-83.636363636363626</v>
       </c>
       <c r="T103" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-83.636363636363626</v>
       </c>
       <c r="U103" s="12">
@@ -12391,10 +12686,13 @@
         <v>170</v>
       </c>
       <c r="AF103" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AG103" s="12"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AG103" s="12">
+        <f t="shared" si="23"/>
+        <v>-0.72600000000000009</v>
+      </c>
       <c r="AH103" s="12"/>
       <c r="AI103" s="12"/>
       <c r="AJ103" s="12"/>
@@ -12442,7 +12740,7 @@
         <v>57</v>
       </c>
       <c r="L104" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>-45</v>
       </c>
       <c r="M104" s="12"/>
@@ -12451,20 +12749,20 @@
         <v>0</v>
       </c>
       <c r="P104" s="12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>2.4</v>
       </c>
       <c r="Q104" s="14"/>
       <c r="R104" s="14">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="S104" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>19.166666666666668</v>
       </c>
       <c r="T104" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>19.166666666666668</v>
       </c>
       <c r="U104" s="12">
@@ -12501,10 +12799,13 @@
         <v>171</v>
       </c>
       <c r="AF104" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AG104" s="12"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AG104" s="12">
+        <f t="shared" si="23"/>
+        <v>0.24</v>
+      </c>
       <c r="AH104" s="12"/>
       <c r="AI104" s="12"/>
       <c r="AJ104" s="12"/>
@@ -12554,7 +12855,7 @@
         <v>180</v>
       </c>
       <c r="L105" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>-130</v>
       </c>
       <c r="M105" s="12"/>
@@ -12563,7 +12864,7 @@
         <v>0</v>
       </c>
       <c r="P105" s="12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>10</v>
       </c>
       <c r="Q105" s="14">
@@ -12571,15 +12872,15 @@
         <v>59</v>
       </c>
       <c r="R105" s="14">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>59</v>
       </c>
       <c r="S105" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>8</v>
       </c>
       <c r="T105" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>2.1</v>
       </c>
       <c r="U105" s="12">
@@ -12616,10 +12917,13 @@
         <v>172</v>
       </c>
       <c r="AF105" s="12">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>5.9</v>
       </c>
-      <c r="AG105" s="12"/>
+      <c r="AG105" s="12">
+        <f t="shared" si="23"/>
+        <v>1</v>
+      </c>
       <c r="AH105" s="12"/>
       <c r="AI105" s="12"/>
       <c r="AJ105" s="12"/>
@@ -12670,7 +12974,7 @@
         <v>233</v>
       </c>
       <c r="L106" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>-31</v>
       </c>
       <c r="M106" s="12"/>
@@ -12679,7 +12983,7 @@
         <v>0</v>
       </c>
       <c r="P106" s="12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>40.4</v>
       </c>
       <c r="Q106" s="14">
@@ -12687,15 +12991,15 @@
         <v>260.39999999999998</v>
       </c>
       <c r="R106" s="14">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>260</v>
       </c>
       <c r="S106" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>10.990099009900991</v>
       </c>
       <c r="T106" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>4.5544554455445549</v>
       </c>
       <c r="U106" s="12">
@@ -12732,10 +13036,13 @@
         <v>159</v>
       </c>
       <c r="AF106" s="12">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>26</v>
       </c>
-      <c r="AG106" s="12"/>
+      <c r="AG106" s="12">
+        <f t="shared" si="23"/>
+        <v>4.04</v>
+      </c>
       <c r="AH106" s="12"/>
       <c r="AI106" s="12"/>
       <c r="AJ106" s="12"/>
@@ -12784,7 +13091,7 @@
         <v>335</v>
       </c>
       <c r="L107" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>-80</v>
       </c>
       <c r="M107" s="12"/>
@@ -12793,7 +13100,7 @@
         <v>0</v>
       </c>
       <c r="P107" s="12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>51</v>
       </c>
       <c r="Q107" s="14">
@@ -12801,15 +13108,15 @@
         <v>312</v>
       </c>
       <c r="R107" s="14">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>312</v>
       </c>
       <c r="S107" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>9</v>
       </c>
       <c r="T107" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>2.8823529411764706</v>
       </c>
       <c r="U107" s="12">
@@ -12846,10 +13153,13 @@
         <v>160</v>
       </c>
       <c r="AF107" s="12">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>31.200000000000003</v>
       </c>
-      <c r="AG107" s="12"/>
+      <c r="AG107" s="12">
+        <f t="shared" si="23"/>
+        <v>5.1000000000000005</v>
+      </c>
       <c r="AH107" s="12"/>
       <c r="AI107" s="12"/>
       <c r="AJ107" s="12"/>
@@ -12899,7 +13209,7 @@
         <v>461</v>
       </c>
       <c r="L108" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>-60</v>
       </c>
       <c r="M108" s="12"/>
@@ -12908,23 +13218,23 @@
         <v>781</v>
       </c>
       <c r="P108" s="12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>80.2</v>
       </c>
       <c r="Q108" s="14">
-        <f t="shared" ref="Q108" si="33">14*P108-O108-F108</f>
+        <f t="shared" ref="Q108" si="35">14*P108-O108-F108</f>
         <v>290.79999999999995</v>
       </c>
       <c r="R108" s="14">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>291</v>
       </c>
       <c r="S108" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>14.002493765586035</v>
       </c>
       <c r="T108" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>10.374064837905237</v>
       </c>
       <c r="U108" s="12">
@@ -12961,10 +13271,13 @@
         <v>162</v>
       </c>
       <c r="AF108" s="12">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>116.4</v>
       </c>
-      <c r="AG108" s="12"/>
+      <c r="AG108" s="12">
+        <f t="shared" si="23"/>
+        <v>32.080000000000005</v>
+      </c>
       <c r="AH108" s="12"/>
       <c r="AI108" s="12"/>
       <c r="AJ108" s="12"/>
@@ -13012,7 +13325,7 @@
         <v>112</v>
       </c>
       <c r="L109" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>-88</v>
       </c>
       <c r="M109" s="12"/>
@@ -13021,20 +13334,20 @@
         <v>0</v>
       </c>
       <c r="P109" s="12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>4.8</v>
       </c>
       <c r="Q109" s="14"/>
       <c r="R109" s="14">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="S109" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>28.125</v>
       </c>
       <c r="T109" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>28.125</v>
       </c>
       <c r="U109" s="12">
@@ -13071,10 +13384,13 @@
         <v>112</v>
       </c>
       <c r="AF109" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AG109" s="12"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AG109" s="12">
+        <f t="shared" si="23"/>
+        <v>0.48</v>
+      </c>
       <c r="AH109" s="12"/>
       <c r="AI109" s="12"/>
       <c r="AJ109" s="12"/>
@@ -13122,7 +13438,7 @@
         <v>115</v>
       </c>
       <c r="L110" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>-88</v>
       </c>
       <c r="M110" s="12"/>
@@ -13131,20 +13447,20 @@
         <v>0</v>
       </c>
       <c r="P110" s="12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>5.4</v>
       </c>
       <c r="Q110" s="14"/>
       <c r="R110" s="14">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="S110" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>24.814814814814813</v>
       </c>
       <c r="T110" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>24.814814814814813</v>
       </c>
       <c r="U110" s="12">
@@ -13181,10 +13497,13 @@
         <v>112</v>
       </c>
       <c r="AF110" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AG110" s="12"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AG110" s="12">
+        <f t="shared" si="23"/>
+        <v>0.54</v>
+      </c>
       <c r="AH110" s="12"/>
       <c r="AI110" s="12"/>
       <c r="AJ110" s="12"/>
@@ -13222,7 +13541,7 @@
       <c r="J111" s="6"/>
       <c r="K111" s="6"/>
       <c r="L111" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="M111" s="6"/>
@@ -13231,20 +13550,20 @@
         <v>0</v>
       </c>
       <c r="P111" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="Q111" s="8"/>
       <c r="R111" s="14">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="S111" s="12" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T111" s="6" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U111" s="6">
@@ -13281,10 +13600,13 @@
         <v>105</v>
       </c>
       <c r="AF111" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AG111" s="12"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AG111" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="AH111" s="12"/>
       <c r="AI111" s="12"/>
       <c r="AJ111" s="12"/>
